--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sase_4010" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.07055</v>
+        <v>-0.0216</v>
       </c>
       <c r="G2">
-        <v>-0.1043409791167409</v>
+        <v>0.05497416020671835</v>
       </c>
       <c r="H2">
-        <v>-0.1043409791167409</v>
+        <v>0.05497416020671835</v>
       </c>
       <c r="I2">
-        <v>-0.2543307086614174</v>
+        <v>-0.0407088122605364</v>
       </c>
       <c r="J2">
-        <v>-0.2543307086614174</v>
+        <v>-0.03562021072796935</v>
       </c>
       <c r="K2">
-        <v>-355.48</v>
+        <v>-69.82600000000001</v>
       </c>
       <c r="L2">
-        <v>-0.6084902430674427</v>
+        <v>-0.07777109507261873</v>
       </c>
       <c r="M2">
-        <v>0.869</v>
+        <v>0.083</v>
       </c>
       <c r="N2">
-        <v>0.0003723541006084498</v>
+        <v>4.139857349493741e-05</v>
       </c>
       <c r="O2">
-        <v>-0.002444581973669405</v>
+        <v>-0.001188668977171827</v>
       </c>
       <c r="P2">
-        <v>0.869</v>
+        <v>0.083</v>
       </c>
       <c r="Q2">
-        <v>0.0003723541006084498</v>
+        <v>4.139857349493741e-05</v>
       </c>
       <c r="R2">
-        <v>-0.002444581973669405</v>
+        <v>-0.001188668977171827</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>188.76</v>
+        <v>138.245</v>
       </c>
       <c r="V2">
-        <v>0.0808809666638101</v>
+        <v>0.06895356376876653</v>
       </c>
       <c r="W2">
-        <v>-0.1911920264598134</v>
+        <v>-0.02480453425037681</v>
       </c>
       <c r="X2">
-        <v>0.07468909605081277</v>
+        <v>0.1157226114342302</v>
       </c>
       <c r="Y2">
-        <v>-0.2658811225106262</v>
+        <v>-0.1405271456846071</v>
       </c>
       <c r="Z2">
-        <v>0.1885148565970519</v>
+        <v>0.2941808650065531</v>
       </c>
       <c r="AA2">
-        <v>-0.06241327919866854</v>
+        <v>-0.02488302846860228</v>
       </c>
       <c r="AB2">
-        <v>0.0596714829146163</v>
+        <v>0.09157835328422423</v>
       </c>
       <c r="AC2">
-        <v>-0.1220847621132848</v>
+        <v>-0.1169514746120911</v>
       </c>
       <c r="AD2">
-        <v>1194.2</v>
+        <v>1133.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1194.2</v>
+        <v>1133.2</v>
       </c>
       <c r="AG2">
-        <v>1005.44</v>
+        <v>994.955</v>
       </c>
       <c r="AH2">
-        <v>0.3384920634920635</v>
+        <v>0.3611102259328893</v>
       </c>
       <c r="AI2">
-        <v>0.3659261529033246</v>
+        <v>0.3646778657398468</v>
       </c>
       <c r="AJ2">
-        <v>0.3010984535403266</v>
+        <v>0.3316676972720348</v>
       </c>
       <c r="AK2">
-        <v>0.327000006504615</v>
+        <v>0.3350970225535548</v>
       </c>
       <c r="AL2">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="AM2">
-        <v>38.213</v>
+        <v>35.96</v>
       </c>
       <c r="AN2">
-        <v>-71.32959025206068</v>
+        <v>10.05661951332067</v>
       </c>
       <c r="AO2">
-        <v>-3.668641975308642</v>
+        <v>-0.9047029702970298</v>
       </c>
       <c r="AP2">
-        <v>-60.05495161868355</v>
+        <v>8.829759855167641</v>
       </c>
       <c r="AQ2">
-        <v>-3.888205584486955</v>
+        <v>-1.016407119021135</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +721,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0311</v>
+        <v>0.0276</v>
       </c>
       <c r="G3">
-        <v>0.211063829787234</v>
+        <v>0.2373239436619718</v>
       </c>
       <c r="H3">
-        <v>0.211063829787234</v>
+        <v>0.2373239436619718</v>
       </c>
       <c r="I3">
-        <v>-0.03778723404255319</v>
+        <v>0.1140845070422535</v>
       </c>
       <c r="J3">
-        <v>-0.03778723404255319</v>
+        <v>0.05704225352112676</v>
       </c>
       <c r="K3">
-        <v>-13.4</v>
+        <v>-1.3</v>
       </c>
       <c r="L3">
-        <v>-0.1140425531914894</v>
+        <v>-0.009154929577464789</v>
       </c>
       <c r="M3">
-        <v>0.869</v>
+        <v>0.083</v>
       </c>
       <c r="N3">
-        <v>0.001049010140028971</v>
+        <v>0.0001586391437308868</v>
       </c>
       <c r="O3">
-        <v>-0.06485074626865671</v>
+        <v>-0.06384615384615384</v>
       </c>
       <c r="P3">
-        <v>0.869</v>
+        <v>0.083</v>
       </c>
       <c r="Q3">
-        <v>0.001049010140028971</v>
+        <v>0.0001586391437308868</v>
       </c>
       <c r="R3">
-        <v>-0.06485074626865671</v>
+        <v>-0.06384615384615384</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +766,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>25.6</v>
+        <v>22.4</v>
       </c>
       <c r="V3">
-        <v>0.03090294543698697</v>
+        <v>0.04281345565749235</v>
       </c>
       <c r="W3">
-        <v>-0.02985074626865672</v>
+        <v>-0.002989192917912164</v>
       </c>
       <c r="X3">
-        <v>0.07596630533171923</v>
+        <v>0.1230841625070398</v>
       </c>
       <c r="Y3">
-        <v>-0.105817051600376</v>
+        <v>-0.126073355424952</v>
       </c>
       <c r="Z3">
-        <v>0.1478731437201107</v>
+        <v>0.1807995925642985</v>
       </c>
       <c r="AA3">
-        <v>-0.005587717090359929</v>
+        <v>0.01031321619556914</v>
       </c>
       <c r="AB3">
-        <v>0.05957355784756745</v>
+        <v>0.09023972845484254</v>
       </c>
       <c r="AC3">
-        <v>-0.06516127493792738</v>
+        <v>-0.07992651225927341</v>
       </c>
       <c r="AD3">
-        <v>376.1</v>
+        <v>377.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>376.1</v>
+        <v>377.7</v>
       </c>
       <c r="AG3">
-        <v>350.5</v>
+        <v>355.3</v>
       </c>
       <c r="AH3">
-        <v>0.3122457451224575</v>
+        <v>0.4192474192474192</v>
       </c>
       <c r="AI3">
-        <v>0.4550514216575923</v>
+        <v>0.4572639225181598</v>
       </c>
       <c r="AJ3">
-        <v>0.2973110526762236</v>
+        <v>0.4044393853158794</v>
       </c>
       <c r="AK3">
-        <v>0.4376326632538394</v>
+        <v>0.4421353907416625</v>
       </c>
       <c r="AL3">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="AM3">
-        <v>11.743</v>
+        <v>12.9</v>
       </c>
       <c r="AN3">
-        <v>17.99521531100479</v>
+        <v>8.643020594965675</v>
       </c>
       <c r="AO3">
-        <v>-0.376271186440678</v>
+        <v>1.255813953488372</v>
       </c>
       <c r="AP3">
-        <v>16.77033492822967</v>
+        <v>8.130434782608695</v>
       </c>
       <c r="AQ3">
-        <v>-0.378097590053649</v>
+        <v>1.255813953488372</v>
       </c>
     </row>
     <row r="4">
@@ -850,25 +852,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.227</v>
+        <v>0.0118</v>
       </c>
       <c r="G4">
-        <v>-0.2765882765882766</v>
+        <v>-0.003269948462768793</v>
       </c>
       <c r="H4">
-        <v>-0.2765882765882766</v>
+        <v>-0.003269948462768793</v>
       </c>
       <c r="I4">
-        <v>-0.3173043173043174</v>
+        <v>-0.06859783188199751</v>
       </c>
       <c r="J4">
-        <v>-0.3173043173043174</v>
+        <v>-0.06859783188199751</v>
       </c>
       <c r="K4">
-        <v>-279.4</v>
+        <v>-41.1</v>
       </c>
       <c r="L4">
-        <v>-0.9806949806949807</v>
+        <v>-0.07304069664119424</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +894,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>78.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="V4">
-        <v>0.07281643227239083</v>
+        <v>0.07287631744887849</v>
       </c>
       <c r="W4">
-        <v>-0.158300283286119</v>
+        <v>-0.0275820414737266</v>
       </c>
       <c r="X4">
-        <v>0.0734118867699063</v>
+        <v>0.1083610603614207</v>
       </c>
       <c r="Y4">
-        <v>-0.2317121700560253</v>
+        <v>-0.1359431018351473</v>
       </c>
       <c r="Z4">
-        <v>0.161005933879627</v>
+        <v>0.3095397885425721</v>
       </c>
       <c r="AA4">
-        <v>-0.05108787793161911</v>
+        <v>-0.02123375837523242</v>
       </c>
       <c r="AB4">
-        <v>0.05959358982257684</v>
+        <v>0.09092853725604752</v>
       </c>
       <c r="AC4">
-        <v>-0.1106814677541959</v>
+        <v>-0.1121622956312799</v>
       </c>
       <c r="AD4">
-        <v>413.4</v>
+        <v>419</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>413.4</v>
+        <v>419</v>
       </c>
       <c r="AG4">
-        <v>334.7</v>
+        <v>338.1</v>
       </c>
       <c r="AH4">
-        <v>0.2766697898541026</v>
+        <v>0.2740173958537702</v>
       </c>
       <c r="AI4">
-        <v>0.2171446580523164</v>
+        <v>0.2271741487746693</v>
       </c>
       <c r="AJ4">
-        <v>0.2364535499823384</v>
+        <v>0.2334622289738987</v>
       </c>
       <c r="AK4">
-        <v>0.1833872116596351</v>
+        <v>0.1917210093563936</v>
       </c>
       <c r="AL4">
-        <v>10.5</v>
+        <v>13.4</v>
       </c>
       <c r="AM4">
-        <v>8.27</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AN4">
-        <v>-15.03272727272727</v>
+        <v>9.33184855233853</v>
       </c>
       <c r="AO4">
-        <v>-8.609523809523811</v>
+        <v>-2.880597014925373</v>
       </c>
       <c r="AP4">
-        <v>-12.17090909090909</v>
+        <v>7.530066815144767</v>
       </c>
       <c r="AQ4">
-        <v>-10.9310761789601</v>
+        <v>-4.308035714285714</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +971,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tourism Enterprises Co. (SASE:4170)</t>
+          <t>Abdulmohsen Al-Hokair Group for Tourism and Development Company (SASE:1820)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,25 +980,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00225</v>
+        <v>-0.0864</v>
       </c>
       <c r="G5">
-        <v>0.02583333333333333</v>
+        <v>0.09305993690851735</v>
       </c>
       <c r="H5">
-        <v>0.02583333333333333</v>
+        <v>0.09305993690851735</v>
       </c>
       <c r="I5">
-        <v>-0.2375</v>
+        <v>-0.06572029442691904</v>
       </c>
       <c r="J5">
-        <v>-0.2375</v>
+        <v>-0.06572029442691904</v>
       </c>
       <c r="K5">
-        <v>-4.28</v>
+        <v>-27.1</v>
       </c>
       <c r="L5">
-        <v>-0.8916666666666667</v>
+        <v>-0.1424815983175605</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1020,67 +1022,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.16</v>
+        <v>34.3</v>
       </c>
       <c r="V5">
-        <v>0.01747899159663865</v>
+        <v>0.2286666666666667</v>
       </c>
       <c r="W5">
-        <v>-0.2240837696335078</v>
+        <v>-0.2383465259454705</v>
       </c>
       <c r="X5">
-        <v>0.05974937600665576</v>
+        <v>0.1881139238383898</v>
       </c>
       <c r="Y5">
-        <v>-0.2838331456401636</v>
+        <v>-0.4264604497838603</v>
       </c>
       <c r="Z5">
-        <v>0.3104786545924967</v>
+        <v>0.4341474549189683</v>
       </c>
       <c r="AA5">
-        <v>-0.07373868046571797</v>
+        <v>-0.02853229856197215</v>
       </c>
       <c r="AB5">
-        <v>0.05974937600665576</v>
+        <v>0.09320835503093004</v>
       </c>
       <c r="AC5">
-        <v>-0.1334880564723737</v>
+        <v>-0.1217406535929022</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>336.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>336.5</v>
       </c>
       <c r="AG5">
-        <v>-4.16</v>
+        <v>302.2</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.6916752312435765</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.7962612399432086</v>
       </c>
       <c r="AJ5">
-        <v>-0.01778994184057475</v>
+        <v>0.6682883679787704</v>
       </c>
       <c r="AK5">
-        <v>-0.3909774436090225</v>
+        <v>0.7782642286891579</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>13.96265560165975</v>
+      </c>
+      <c r="AO5">
+        <v>-0.8865248226950355</v>
       </c>
       <c r="AP5">
-        <v>-9.08296943231441</v>
+        <v>12.53941908713693</v>
+      </c>
+      <c r="AQ5">
+        <v>-0.8865248226950355</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1099,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abdulmohsen Al-Hokair Group for Tourism and Development Company (SASE:1820)</t>
+          <t>Tourism Enterprises Co. (SASE:4170)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,25 +1108,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.11</v>
+        <v>-0.055</v>
       </c>
       <c r="G6">
-        <v>-0.04</v>
+        <v>-0.06870748299319729</v>
       </c>
       <c r="H6">
-        <v>-0.04</v>
+        <v>-0.06870748299319729</v>
       </c>
       <c r="I6">
-        <v>-0.2971751412429379</v>
+        <v>-0.5612244897959183</v>
       </c>
       <c r="J6">
-        <v>-0.2971751412429379</v>
+        <v>-0.5612244897959183</v>
       </c>
       <c r="K6">
-        <v>-58.4</v>
+        <v>-0.326</v>
       </c>
       <c r="L6">
-        <v>-0.3299435028248587</v>
+        <v>-0.1108843537414966</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1142,73 +1150,8779 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>80.3</v>
+        <v>0.645</v>
       </c>
       <c r="V6">
-        <v>0.4303322615219721</v>
+        <v>0.002910649819494585</v>
       </c>
       <c r="W6">
-        <v>-0.6547085201793722</v>
+        <v>-0.02202702702702703</v>
       </c>
       <c r="X6">
-        <v>0.1372181968850848</v>
+        <v>0.09222816931240094</v>
       </c>
       <c r="Y6">
-        <v>-0.7919267170644571</v>
+        <v>-0.114255196339428</v>
       </c>
       <c r="Z6">
-        <v>0.3407778205621871</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="AA6">
-        <v>-0.1012706969580285</v>
+        <v>-0.1550751879699248</v>
       </c>
       <c r="AB6">
-        <v>0.06189243275788972</v>
+        <v>0.09222816931240094</v>
       </c>
       <c r="AC6">
-        <v>-0.1631631297159182</v>
+        <v>-0.2473033572823257</v>
       </c>
       <c r="AD6">
-        <v>404.7</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>404.7</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>324.4</v>
+        <v>-0.645</v>
       </c>
       <c r="AH6">
-        <v>0.6844241501775749</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.7806712962962963</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.6348336594911937</v>
+        <v>-0.002919146432531511</v>
       </c>
       <c r="AK6">
-        <v>0.7404702122803013</v>
+        <v>-0.04689203925845147</v>
       </c>
       <c r="AL6">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>-38.17924528301887</v>
-      </c>
-      <c r="AO6">
-        <v>-2.890109890109891</v>
+        <v>-0</v>
       </c>
       <c r="AP6">
-        <v>-30.60377358490566</v>
-      </c>
-      <c r="AQ6">
-        <v>-2.890109890109891</v>
+        <v>35.83333333333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dur Hospitality Company (SASE:4010)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SASE:4010</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.419247419247419</v>
+      </c>
+      <c r="F2">
+        <v>0.03</v>
+      </c>
+      <c r="G2">
+        <v>523.2</v>
+      </c>
+      <c r="H2">
+        <v>847.3613182431141</v>
+      </c>
+      <c r="I2">
+        <v>878.5</v>
+      </c>
+      <c r="J2">
+        <v>851.988318243114</v>
+      </c>
+      <c r="K2">
+        <v>377.7</v>
+      </c>
+      <c r="L2">
+        <v>27.027</v>
+      </c>
+      <c r="M2">
+        <v>0.0902397284548425</v>
+      </c>
+      <c r="N2">
+        <v>0.0918404002965265</v>
+      </c>
+      <c r="O2">
+        <v>0.044742752293578</v>
+      </c>
+      <c r="P2">
+        <v>0.03656</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.12308416250704</v>
+      </c>
+      <c r="T2">
+        <v>0.09355010339848099</v>
+      </c>
+      <c r="U2">
+        <v>1.18187576859684</v>
+      </c>
+      <c r="V2">
+        <v>0.767734039350889</v>
+      </c>
+      <c r="W2">
+        <v>13.11598685778117</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>523.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.05592844036697248</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>43.7</v>
+      </c>
+      <c r="AH2">
+        <v>27.5</v>
+      </c>
+      <c r="AI2">
+        <v>69.70000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>377.7</v>
+      </c>
+      <c r="AK2">
+        <v>377.7</v>
+      </c>
+      <c r="AL2">
+        <v>12.9</v>
+      </c>
+      <c r="AM2">
+        <v>377.7</v>
+      </c>
+      <c r="AN2">
+        <v>22.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09222816931240094</v>
+      </c>
+      <c r="C2">
+        <v>868.2047885442036</v>
+      </c>
+      <c r="D2">
+        <v>845.8047885442036</v>
+      </c>
+      <c r="E2">
+        <v>-377.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>22.4</v>
+      </c>
+      <c r="H2">
+        <v>523.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>43.7</v>
+      </c>
+      <c r="K2">
+        <v>27.5</v>
+      </c>
+      <c r="L2">
+        <v>16.2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>16.2</v>
+      </c>
+      <c r="O2">
+        <v>3.239999999999999</v>
+      </c>
+      <c r="P2">
+        <v>12.96</v>
+      </c>
+      <c r="Q2">
+        <v>40.46000000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09222816931240094</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09209891297377612</v>
+      </c>
+      <c r="C3">
+        <v>861.2469679033838</v>
+      </c>
+      <c r="D3">
+        <v>847.8559679033839</v>
+      </c>
+      <c r="E3">
+        <v>-368.691</v>
+      </c>
+      <c r="F3">
+        <v>9.009</v>
+      </c>
+      <c r="G3">
+        <v>22.4</v>
+      </c>
+      <c r="H3">
+        <v>523.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>43.7</v>
+      </c>
+      <c r="K3">
+        <v>27.5</v>
+      </c>
+      <c r="L3">
+        <v>16.2</v>
+      </c>
+      <c r="M3">
+        <v>0.4117113000000001</v>
+      </c>
+      <c r="N3">
+        <v>15.7882887</v>
+      </c>
+      <c r="O3">
+        <v>3.157657739999999</v>
+      </c>
+      <c r="P3">
+        <v>12.63063096</v>
+      </c>
+      <c r="Q3">
+        <v>40.13063096</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09265991209472337</v>
+      </c>
+      <c r="T3">
+        <v>0.7552513201776532</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>39.3479605733435</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09196965663515132</v>
+      </c>
+      <c r="C4">
+        <v>854.2991201663068</v>
+      </c>
+      <c r="D4">
+        <v>849.9171201663069</v>
+      </c>
+      <c r="E4">
+        <v>-359.682</v>
+      </c>
+      <c r="F4">
+        <v>18.018</v>
+      </c>
+      <c r="G4">
+        <v>22.4</v>
+      </c>
+      <c r="H4">
+        <v>523.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>43.7</v>
+      </c>
+      <c r="K4">
+        <v>27.5</v>
+      </c>
+      <c r="L4">
+        <v>16.2</v>
+      </c>
+      <c r="M4">
+        <v>0.8234226000000001</v>
+      </c>
+      <c r="N4">
+        <v>15.3765774</v>
+      </c>
+      <c r="O4">
+        <v>3.075315479999999</v>
+      </c>
+      <c r="P4">
+        <v>12.30126192</v>
+      </c>
+      <c r="Q4">
+        <v>39.80126192</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09310046595423604</v>
+      </c>
+      <c r="T4">
+        <v>0.7614289924215504</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>19.67398028667175</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09184040029652651</v>
+      </c>
+      <c r="C5">
+        <v>847.3613182431137</v>
+      </c>
+      <c r="D5">
+        <v>851.9883182431138</v>
+      </c>
+      <c r="E5">
+        <v>-350.673</v>
+      </c>
+      <c r="F5">
+        <v>27.027</v>
+      </c>
+      <c r="G5">
+        <v>22.4</v>
+      </c>
+      <c r="H5">
+        <v>523.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>43.7</v>
+      </c>
+      <c r="K5">
+        <v>27.5</v>
+      </c>
+      <c r="L5">
+        <v>16.2</v>
+      </c>
+      <c r="M5">
+        <v>1.2351339</v>
+      </c>
+      <c r="N5">
+        <v>14.9648661</v>
+      </c>
+      <c r="O5">
+        <v>2.992973219999999</v>
+      </c>
+      <c r="P5">
+        <v>11.97189288</v>
+      </c>
+      <c r="Q5">
+        <v>39.47189288</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09355010339848095</v>
+      </c>
+      <c r="T5">
+        <v>0.7677340393508887</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>13.11598685778117</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09188394395790174</v>
+      </c>
+      <c r="C6">
+        <v>837.653449846021</v>
+      </c>
+      <c r="D6">
+        <v>851.2894498460209</v>
+      </c>
+      <c r="E6">
+        <v>-341.664</v>
+      </c>
+      <c r="F6">
+        <v>36.036</v>
+      </c>
+      <c r="G6">
+        <v>22.4</v>
+      </c>
+      <c r="H6">
+        <v>523.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>43.7</v>
+      </c>
+      <c r="K6">
+        <v>27.5</v>
+      </c>
+      <c r="L6">
+        <v>16.2</v>
+      </c>
+      <c r="M6">
+        <v>1.8414396</v>
+      </c>
+      <c r="N6">
+        <v>14.3585604</v>
+      </c>
+      <c r="O6">
+        <v>2.87171208</v>
+      </c>
+      <c r="P6">
+        <v>11.48684832</v>
+      </c>
+      <c r="Q6">
+        <v>38.98684832000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09400910828948097</v>
+      </c>
+      <c r="T6">
+        <v>0.7741704414245885</v>
+      </c>
+      <c r="U6">
+        <v>0.0511</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.04088</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>8.797464766153611</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09187388761927691</v>
+      </c>
+      <c r="C7">
+        <v>828.8057505413235</v>
+      </c>
+      <c r="D7">
+        <v>851.4507505413235</v>
+      </c>
+      <c r="E7">
+        <v>-332.655</v>
+      </c>
+      <c r="F7">
+        <v>45.04500000000001</v>
+      </c>
+      <c r="G7">
+        <v>22.4</v>
+      </c>
+      <c r="H7">
+        <v>523.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>43.7</v>
+      </c>
+      <c r="K7">
+        <v>27.5</v>
+      </c>
+      <c r="L7">
+        <v>16.2</v>
+      </c>
+      <c r="M7">
+        <v>2.387385000000001</v>
+      </c>
+      <c r="N7">
+        <v>13.812615</v>
+      </c>
+      <c r="O7">
+        <v>2.762522999999999</v>
+      </c>
+      <c r="P7">
+        <v>11.050092</v>
+      </c>
+      <c r="Q7">
+        <v>38.55009200000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09447777644134413</v>
+      </c>
+      <c r="T7">
+        <v>0.7807423466998394</v>
+      </c>
+      <c r="U7">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>6.785667163025652</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09189903128065212</v>
+      </c>
+      <c r="C8">
+        <v>819.3935682452826</v>
+      </c>
+      <c r="D8">
+        <v>851.0475682452826</v>
+      </c>
+      <c r="E8">
+        <v>-323.646</v>
+      </c>
+      <c r="F8">
+        <v>54.054</v>
+      </c>
+      <c r="G8">
+        <v>22.4</v>
+      </c>
+      <c r="H8">
+        <v>523.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>43.7</v>
+      </c>
+      <c r="K8">
+        <v>27.5</v>
+      </c>
+      <c r="L8">
+        <v>16.2</v>
+      </c>
+      <c r="M8">
+        <v>2.97297</v>
+      </c>
+      <c r="N8">
+        <v>13.22703</v>
+      </c>
+      <c r="O8">
+        <v>2.645405999999999</v>
+      </c>
+      <c r="P8">
+        <v>10.581624</v>
+      </c>
+      <c r="Q8">
+        <v>38.08162400000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09495641625601289</v>
+      </c>
+      <c r="T8">
+        <v>0.7874540797469046</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.044</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>5.449096358187266</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09184417494202732</v>
+      </c>
+      <c r="C9">
+        <v>811.2646904008351</v>
+      </c>
+      <c r="D9">
+        <v>851.9276904008351</v>
+      </c>
+      <c r="E9">
+        <v>-314.637</v>
+      </c>
+      <c r="F9">
+        <v>63.06300000000001</v>
+      </c>
+      <c r="G9">
+        <v>22.4</v>
+      </c>
+      <c r="H9">
+        <v>523.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>43.7</v>
+      </c>
+      <c r="K9">
+        <v>27.5</v>
+      </c>
+      <c r="L9">
+        <v>16.2</v>
+      </c>
+      <c r="M9">
+        <v>3.468465000000001</v>
+      </c>
+      <c r="N9">
+        <v>12.731535</v>
+      </c>
+      <c r="O9">
+        <v>2.546306999999999</v>
+      </c>
+      <c r="P9">
+        <v>10.185228</v>
+      </c>
+      <c r="Q9">
+        <v>37.685228</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09544534940002938</v>
+      </c>
+      <c r="T9">
+        <v>0.7943101511390678</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.044</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>4.67065402130337</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09230131860340252</v>
+      </c>
+      <c r="C10">
+        <v>794.9763680629368</v>
+      </c>
+      <c r="D10">
+        <v>844.6483680629368</v>
+      </c>
+      <c r="E10">
+        <v>-305.628</v>
+      </c>
+      <c r="F10">
+        <v>72.072</v>
+      </c>
+      <c r="G10">
+        <v>22.4</v>
+      </c>
+      <c r="H10">
+        <v>523.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>43.7</v>
+      </c>
+      <c r="K10">
+        <v>27.5</v>
+      </c>
+      <c r="L10">
+        <v>16.2</v>
+      </c>
+      <c r="M10">
+        <v>4.540536</v>
+      </c>
+      <c r="N10">
+        <v>11.659464</v>
+      </c>
+      <c r="O10">
+        <v>2.331892799999999</v>
+      </c>
+      <c r="P10">
+        <v>9.327571200000001</v>
+      </c>
+      <c r="Q10">
+        <v>36.82757120000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09594491152543752</v>
+      </c>
+      <c r="T10">
+        <v>0.8013152675614954</v>
+      </c>
+      <c r="U10">
+        <v>0.063</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.0504</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>3.567860710717853</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09435526226477771</v>
+      </c>
+      <c r="C11">
+        <v>754.7397202947492</v>
+      </c>
+      <c r="D11">
+        <v>813.4207202947492</v>
+      </c>
+      <c r="E11">
+        <v>-296.619</v>
+      </c>
+      <c r="F11">
+        <v>81.081</v>
+      </c>
+      <c r="G11">
+        <v>22.4</v>
+      </c>
+      <c r="H11">
+        <v>523.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>43.7</v>
+      </c>
+      <c r="K11">
+        <v>27.5</v>
+      </c>
+      <c r="L11">
+        <v>16.2</v>
+      </c>
+      <c r="M11">
+        <v>7.410803400000001</v>
+      </c>
+      <c r="N11">
+        <v>8.789196599999999</v>
+      </c>
+      <c r="O11">
+        <v>1.757839319999999</v>
+      </c>
+      <c r="P11">
+        <v>7.031357279999999</v>
+      </c>
+      <c r="Q11">
+        <v>34.53135728</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09645545303821726</v>
+      </c>
+      <c r="T11">
+        <v>0.8084743425866137</v>
+      </c>
+      <c r="U11">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.07312</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>2.185997809630194</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09627960592615292</v>
+      </c>
+      <c r="C12">
+        <v>718.4984353493462</v>
+      </c>
+      <c r="D12">
+        <v>786.1884353493463</v>
+      </c>
+      <c r="E12">
+        <v>-287.61</v>
+      </c>
+      <c r="F12">
+        <v>90.09000000000002</v>
+      </c>
+      <c r="G12">
+        <v>22.4</v>
+      </c>
+      <c r="H12">
+        <v>523.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>43.7</v>
+      </c>
+      <c r="K12">
+        <v>27.5</v>
+      </c>
+      <c r="L12">
+        <v>16.2</v>
+      </c>
+      <c r="M12">
+        <v>10.135125</v>
+      </c>
+      <c r="N12">
+        <v>6.064874999999997</v>
+      </c>
+      <c r="O12">
+        <v>1.212974999999999</v>
+      </c>
+      <c r="P12">
+        <v>4.851899999999998</v>
+      </c>
+      <c r="Q12">
+        <v>32.3519</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09697733991794769</v>
+      </c>
+      <c r="T12">
+        <v>0.8157925081678459</v>
+      </c>
+      <c r="U12">
+        <v>0.1125</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>1.598401598401598</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1050124042700951</v>
+      </c>
+      <c r="C13">
+        <v>605.7985160732713</v>
+      </c>
+      <c r="D13">
+        <v>682.4975160732714</v>
+      </c>
+      <c r="E13">
+        <v>-278.601</v>
+      </c>
+      <c r="F13">
+        <v>99.099</v>
+      </c>
+      <c r="G13">
+        <v>22.4</v>
+      </c>
+      <c r="H13">
+        <v>523.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>43.7</v>
+      </c>
+      <c r="K13">
+        <v>27.5</v>
+      </c>
+      <c r="L13">
+        <v>16.2</v>
+      </c>
+      <c r="M13">
+        <v>19.4828634</v>
+      </c>
+      <c r="N13">
+        <v>-3.2828634</v>
+      </c>
+      <c r="O13">
+        <v>-0.6565726799999999</v>
+      </c>
+      <c r="P13">
+        <v>-2.62629072</v>
+      </c>
+      <c r="Q13">
+        <v>24.87370928</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09773349198483</v>
+      </c>
+      <c r="T13">
+        <v>0.8263956603928915</v>
+      </c>
+      <c r="U13">
+        <v>0.1966</v>
+      </c>
+      <c r="V13">
+        <v>0.1662999905855727</v>
+      </c>
+      <c r="W13">
+        <v>0.1639054218508764</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.8314999529278637</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1087330320384277</v>
+      </c>
+      <c r="C14">
+        <v>560.4787894237402</v>
+      </c>
+      <c r="D14">
+        <v>646.1867894237402</v>
+      </c>
+      <c r="E14">
+        <v>-269.592</v>
+      </c>
+      <c r="F14">
+        <v>108.108</v>
+      </c>
+      <c r="G14">
+        <v>22.4</v>
+      </c>
+      <c r="H14">
+        <v>523.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>43.7</v>
+      </c>
+      <c r="K14">
+        <v>27.5</v>
+      </c>
+      <c r="L14">
+        <v>16.2</v>
+      </c>
+      <c r="M14">
+        <v>23.1134904</v>
+      </c>
+      <c r="N14">
+        <v>-6.913490400000001</v>
+      </c>
+      <c r="O14">
+        <v>-1.38269808</v>
+      </c>
+      <c r="P14">
+        <v>-5.530792320000001</v>
+      </c>
+      <c r="Q14">
+        <v>21.96920768</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09849254049412652</v>
+      </c>
+      <c r="T14">
+        <v>0.8370394280194866</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.1401778763799343</v>
+      </c>
+      <c r="W14">
+        <v>0.18382997002997</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.7008893818996719</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1104830320384277</v>
+      </c>
+      <c r="C15">
+        <v>535.6944120529095</v>
+      </c>
+      <c r="D15">
+        <v>630.4114120529094</v>
+      </c>
+      <c r="E15">
+        <v>-260.583</v>
+      </c>
+      <c r="F15">
+        <v>117.117</v>
+      </c>
+      <c r="G15">
+        <v>22.4</v>
+      </c>
+      <c r="H15">
+        <v>523.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>43.7</v>
+      </c>
+      <c r="K15">
+        <v>27.5</v>
+      </c>
+      <c r="L15">
+        <v>16.2</v>
+      </c>
+      <c r="M15">
+        <v>25.0396146</v>
+      </c>
+      <c r="N15">
+        <v>-8.839614600000004</v>
+      </c>
+      <c r="O15">
+        <v>-1.76792292</v>
+      </c>
+      <c r="P15">
+        <v>-7.071691680000004</v>
+      </c>
+      <c r="Q15">
+        <v>20.42830832</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09917866164923142</v>
+      </c>
+      <c r="T15">
+        <v>0.8466605708702853</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1293949628122471</v>
+      </c>
+      <c r="W15">
+        <v>0.1861353569507416</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.6469748140612355</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1122330320384277</v>
+      </c>
+      <c r="C16">
+        <v>511.661928200094</v>
+      </c>
+      <c r="D16">
+        <v>615.3879282000941</v>
+      </c>
+      <c r="E16">
+        <v>-251.574</v>
+      </c>
+      <c r="F16">
+        <v>126.126</v>
+      </c>
+      <c r="G16">
+        <v>22.4</v>
+      </c>
+      <c r="H16">
+        <v>523.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>43.7</v>
+      </c>
+      <c r="K16">
+        <v>27.5</v>
+      </c>
+      <c r="L16">
+        <v>16.2</v>
+      </c>
+      <c r="M16">
+        <v>26.9657388</v>
+      </c>
+      <c r="N16">
+        <v>-10.7657388</v>
+      </c>
+      <c r="O16">
+        <v>-2.15314776</v>
+      </c>
+      <c r="P16">
+        <v>-8.612591040000005</v>
+      </c>
+      <c r="Q16">
+        <v>18.88740896</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.099880739110269</v>
+      </c>
+      <c r="T16">
+        <v>0.8565054612292421</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1201524654685151</v>
+      </c>
+      <c r="W16">
+        <v>0.1881114028828315</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.6007623273425757</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1139830320384277</v>
+      </c>
+      <c r="C17">
+        <v>488.3288334522297</v>
+      </c>
+      <c r="D17">
+        <v>601.0638334522297</v>
+      </c>
+      <c r="E17">
+        <v>-242.565</v>
+      </c>
+      <c r="F17">
+        <v>135.135</v>
+      </c>
+      <c r="G17">
+        <v>22.4</v>
+      </c>
+      <c r="H17">
+        <v>523.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>43.7</v>
+      </c>
+      <c r="K17">
+        <v>27.5</v>
+      </c>
+      <c r="L17">
+        <v>16.2</v>
+      </c>
+      <c r="M17">
+        <v>28.891863</v>
+      </c>
+      <c r="N17">
+        <v>-12.69186300000001</v>
+      </c>
+      <c r="O17">
+        <v>-2.538372600000001</v>
+      </c>
+      <c r="P17">
+        <v>-10.1534904</v>
+      </c>
+      <c r="Q17">
+        <v>17.3465096</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.100599336040978</v>
+      </c>
+      <c r="T17">
+        <v>0.8665819960672332</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1121423011039474</v>
+      </c>
+      <c r="W17">
+        <v>0.189823976023976</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.5607115055197374</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1157330320384277</v>
+      </c>
+      <c r="C18">
+        <v>465.6474006795813</v>
+      </c>
+      <c r="D18">
+        <v>587.3914006795814</v>
+      </c>
+      <c r="E18">
+        <v>-233.556</v>
+      </c>
+      <c r="F18">
+        <v>144.144</v>
+      </c>
+      <c r="G18">
+        <v>22.4</v>
+      </c>
+      <c r="H18">
+        <v>523.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>43.7</v>
+      </c>
+      <c r="K18">
+        <v>27.5</v>
+      </c>
+      <c r="L18">
+        <v>16.2</v>
+      </c>
+      <c r="M18">
+        <v>30.8179872</v>
+      </c>
+      <c r="N18">
+        <v>-14.6179872</v>
+      </c>
+      <c r="O18">
+        <v>-2.92359744</v>
+      </c>
+      <c r="P18">
+        <v>-11.69438976</v>
+      </c>
+      <c r="Q18">
+        <v>15.80561024</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1013350424224183</v>
+      </c>
+      <c r="T18">
+        <v>0.8768984484013669</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1051334072849508</v>
+      </c>
+      <c r="W18">
+        <v>0.1913224775224775</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5256670364247539</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1218271205725117</v>
+      </c>
+      <c r="C19">
+        <v>413.5245943086296</v>
+      </c>
+      <c r="D19">
+        <v>544.2775943086297</v>
+      </c>
+      <c r="E19">
+        <v>-224.547</v>
+      </c>
+      <c r="F19">
+        <v>153.153</v>
+      </c>
+      <c r="G19">
+        <v>22.4</v>
+      </c>
+      <c r="H19">
+        <v>523.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>43.7</v>
+      </c>
+      <c r="K19">
+        <v>27.5</v>
+      </c>
+      <c r="L19">
+        <v>16.2</v>
+      </c>
+      <c r="M19">
+        <v>36.5729364</v>
+      </c>
+      <c r="N19">
+        <v>-20.3729364</v>
+      </c>
+      <c r="O19">
+        <v>-4.07458728</v>
+      </c>
+      <c r="P19">
+        <v>-16.29834912</v>
+      </c>
+      <c r="Q19">
+        <v>11.20165088</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1022018363480907</v>
+      </c>
+      <c r="T19">
+        <v>0.8890530775350858</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.08859009745796619</v>
+      </c>
+      <c r="W19">
+        <v>0.2176446847270377</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.442950487289831</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1238271205725117</v>
+      </c>
+      <c r="C20">
+        <v>391.713147497686</v>
+      </c>
+      <c r="D20">
+        <v>531.4751474976861</v>
+      </c>
+      <c r="E20">
+        <v>-215.538</v>
+      </c>
+      <c r="F20">
+        <v>162.162</v>
+      </c>
+      <c r="G20">
+        <v>22.4</v>
+      </c>
+      <c r="H20">
+        <v>523.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>43.7</v>
+      </c>
+      <c r="K20">
+        <v>27.5</v>
+      </c>
+      <c r="L20">
+        <v>16.2</v>
+      </c>
+      <c r="M20">
+        <v>38.7242856</v>
+      </c>
+      <c r="N20">
+        <v>-22.5242856</v>
+      </c>
+      <c r="O20">
+        <v>-4.50485712</v>
+      </c>
+      <c r="P20">
+        <v>-18.01942848</v>
+      </c>
+      <c r="Q20">
+        <v>9.480571520000002</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1029750294742869</v>
+      </c>
+      <c r="T20">
+        <v>0.8998951882367332</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.08366842537696806</v>
+      </c>
+      <c r="W20">
+        <v>0.21881998001998</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.4183421268848404</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1258271205725117</v>
+      </c>
+      <c r="C21">
+        <v>370.4901354977172</v>
+      </c>
+      <c r="D21">
+        <v>519.2611354977173</v>
+      </c>
+      <c r="E21">
+        <v>-206.529</v>
+      </c>
+      <c r="F21">
+        <v>171.171</v>
+      </c>
+      <c r="G21">
+        <v>22.4</v>
+      </c>
+      <c r="H21">
+        <v>523.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>43.7</v>
+      </c>
+      <c r="K21">
+        <v>27.5</v>
+      </c>
+      <c r="L21">
+        <v>16.2</v>
+      </c>
+      <c r="M21">
+        <v>40.87563480000001</v>
+      </c>
+      <c r="N21">
+        <v>-24.67563480000001</v>
+      </c>
+      <c r="O21">
+        <v>-4.935126960000001</v>
+      </c>
+      <c r="P21">
+        <v>-19.74050784000001</v>
+      </c>
+      <c r="Q21">
+        <v>7.759492159999997</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1037673137887843</v>
+      </c>
+      <c r="T21">
+        <v>0.9110050053754583</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.07926482404133817</v>
+      </c>
+      <c r="W21">
+        <v>0.2198715600189285</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3963241202066908</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1278271205725117</v>
+      </c>
+      <c r="C22">
+        <v>349.8159006308931</v>
+      </c>
+      <c r="D22">
+        <v>507.5959006308931</v>
+      </c>
+      <c r="E22">
+        <v>-197.52</v>
+      </c>
+      <c r="F22">
+        <v>180.18</v>
+      </c>
+      <c r="G22">
+        <v>22.4</v>
+      </c>
+      <c r="H22">
+        <v>523.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>43.7</v>
+      </c>
+      <c r="K22">
+        <v>27.5</v>
+      </c>
+      <c r="L22">
+        <v>16.2</v>
+      </c>
+      <c r="M22">
+        <v>43.02698400000001</v>
+      </c>
+      <c r="N22">
+        <v>-26.82698400000001</v>
+      </c>
+      <c r="O22">
+        <v>-5.365396800000002</v>
+      </c>
+      <c r="P22">
+        <v>-21.46158720000001</v>
+      </c>
+      <c r="Q22">
+        <v>6.038412799999993</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1045794052111441</v>
+      </c>
+      <c r="T22">
+        <v>0.9223925679426515</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.07530158283927124</v>
+      </c>
+      <c r="W22">
+        <v>0.220817982017982</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3765079141963563</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1298271205725117</v>
+      </c>
+      <c r="C23">
+        <v>329.6542705699094</v>
+      </c>
+      <c r="D23">
+        <v>496.4432705699095</v>
+      </c>
+      <c r="E23">
+        <v>-188.511</v>
+      </c>
+      <c r="F23">
+        <v>189.189</v>
+      </c>
+      <c r="G23">
+        <v>22.4</v>
+      </c>
+      <c r="H23">
+        <v>523.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>43.7</v>
+      </c>
+      <c r="K23">
+        <v>27.5</v>
+      </c>
+      <c r="L23">
+        <v>16.2</v>
+      </c>
+      <c r="M23">
+        <v>45.1783332</v>
+      </c>
+      <c r="N23">
+        <v>-28.97833320000001</v>
+      </c>
+      <c r="O23">
+        <v>-5.795666639999999</v>
+      </c>
+      <c r="P23">
+        <v>-23.18266656</v>
+      </c>
+      <c r="Q23">
+        <v>4.317333439999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1054120559100193</v>
+      </c>
+      <c r="T23">
+        <v>0.9340684232330648</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.07171579318025834</v>
+      </c>
+      <c r="W23">
+        <v>0.2216742685885543</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3585789659012918</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1318271205725117</v>
+      </c>
+      <c r="C24">
+        <v>309.9721836783734</v>
+      </c>
+      <c r="D24">
+        <v>485.7701836783734</v>
+      </c>
+      <c r="E24">
+        <v>-179.502</v>
+      </c>
+      <c r="F24">
+        <v>198.198</v>
+      </c>
+      <c r="G24">
+        <v>22.4</v>
+      </c>
+      <c r="H24">
+        <v>523.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>43.7</v>
+      </c>
+      <c r="K24">
+        <v>27.5</v>
+      </c>
+      <c r="L24">
+        <v>16.2</v>
+      </c>
+      <c r="M24">
+        <v>47.3296824</v>
+      </c>
+      <c r="N24">
+        <v>-31.1296824</v>
+      </c>
+      <c r="O24">
+        <v>-6.22593648</v>
+      </c>
+      <c r="P24">
+        <v>-24.90374592000001</v>
+      </c>
+      <c r="Q24">
+        <v>2.596254079999998</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1062660566268144</v>
+      </c>
+      <c r="T24">
+        <v>0.9460436594283606</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.06845598439933751</v>
+      </c>
+      <c r="W24">
+        <v>0.2224527109254382</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3422799219966876</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1338271205725117</v>
+      </c>
+      <c r="C25">
+        <v>290.7393616631056</v>
+      </c>
+      <c r="D25">
+        <v>475.5463616631056</v>
+      </c>
+      <c r="E25">
+        <v>-170.493</v>
+      </c>
+      <c r="F25">
+        <v>207.207</v>
+      </c>
+      <c r="G25">
+        <v>22.4</v>
+      </c>
+      <c r="H25">
+        <v>523.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>43.7</v>
+      </c>
+      <c r="K25">
+        <v>27.5</v>
+      </c>
+      <c r="L25">
+        <v>16.2</v>
+      </c>
+      <c r="M25">
+        <v>49.48103160000001</v>
+      </c>
+      <c r="N25">
+        <v>-33.28103160000001</v>
+      </c>
+      <c r="O25">
+        <v>-6.65620632</v>
+      </c>
+      <c r="P25">
+        <v>-26.62482528000001</v>
+      </c>
+      <c r="Q25">
+        <v>0.8751747199999969</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1071422391804094</v>
+      </c>
+      <c r="T25">
+        <v>0.9583299407196378</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.06547963725154023</v>
+      </c>
+      <c r="W25">
+        <v>0.2231634626243322</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3273981862577012</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1358271205725117</v>
+      </c>
+      <c r="C26">
+        <v>271.9280227117458</v>
+      </c>
+      <c r="D26">
+        <v>465.7440227117459</v>
+      </c>
+      <c r="E26">
+        <v>-161.484</v>
+      </c>
+      <c r="F26">
+        <v>216.216</v>
+      </c>
+      <c r="G26">
+        <v>22.4</v>
+      </c>
+      <c r="H26">
+        <v>523.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>43.7</v>
+      </c>
+      <c r="K26">
+        <v>27.5</v>
+      </c>
+      <c r="L26">
+        <v>16.2</v>
+      </c>
+      <c r="M26">
+        <v>51.63238080000001</v>
+      </c>
+      <c r="N26">
+        <v>-35.4323808</v>
+      </c>
+      <c r="O26">
+        <v>-7.086476159999999</v>
+      </c>
+      <c r="P26">
+        <v>-28.34590464</v>
+      </c>
+      <c r="Q26">
+        <v>-0.8459046400000005</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1080414791696253</v>
+      </c>
+      <c r="T26">
+        <v>0.970939545202791</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.06275131903272604</v>
+      </c>
+      <c r="W26">
+        <v>0.223814985014985</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3137565951636303</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1378271205725117</v>
+      </c>
+      <c r="C27">
+        <v>253.5126293920348</v>
+      </c>
+      <c r="D27">
+        <v>456.3376293920348</v>
+      </c>
+      <c r="E27">
+        <v>-152.475</v>
+      </c>
+      <c r="F27">
+        <v>225.225</v>
+      </c>
+      <c r="G27">
+        <v>22.4</v>
+      </c>
+      <c r="H27">
+        <v>523.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>43.7</v>
+      </c>
+      <c r="K27">
+        <v>27.5</v>
+      </c>
+      <c r="L27">
+        <v>16.2</v>
+      </c>
+      <c r="M27">
+        <v>53.78373000000001</v>
+      </c>
+      <c r="N27">
+        <v>-37.58373</v>
+      </c>
+      <c r="O27">
+        <v>-7.516745999999999</v>
+      </c>
+      <c r="P27">
+        <v>-30.06698400000001</v>
+      </c>
+      <c r="Q27">
+        <v>-2.566984000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.108964698891887</v>
+      </c>
+      <c r="T27">
+        <v>0.983885405805495</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.060241266271417</v>
+      </c>
+      <c r="W27">
+        <v>0.2244143856143856</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3012063313570852</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1398271205725117</v>
+      </c>
+      <c r="C28">
+        <v>235.4696664956162</v>
+      </c>
+      <c r="D28">
+        <v>447.3036664956163</v>
+      </c>
+      <c r="E28">
+        <v>-143.466</v>
+      </c>
+      <c r="F28">
+        <v>234.234</v>
+      </c>
+      <c r="G28">
+        <v>22.4</v>
+      </c>
+      <c r="H28">
+        <v>523.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>43.7</v>
+      </c>
+      <c r="K28">
+        <v>27.5</v>
+      </c>
+      <c r="L28">
+        <v>16.2</v>
+      </c>
+      <c r="M28">
+        <v>55.93507920000001</v>
+      </c>
+      <c r="N28">
+        <v>-39.73507920000002</v>
+      </c>
+      <c r="O28">
+        <v>-7.947015840000001</v>
+      </c>
+      <c r="P28">
+        <v>-31.78806336000001</v>
+      </c>
+      <c r="Q28">
+        <v>-4.28806336000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1099128704985341</v>
+      </c>
+      <c r="T28">
+        <v>0.9971811545325961</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.05792429449174712</v>
+      </c>
+      <c r="W28">
+        <v>0.2249676784753708</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2896214724587356</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1418271205725117</v>
+      </c>
+      <c r="C29">
+        <v>217.7774447573012</v>
+      </c>
+      <c r="D29">
+        <v>438.6204447573013</v>
+      </c>
+      <c r="E29">
+        <v>-134.4569999999999</v>
+      </c>
+      <c r="F29">
+        <v>243.2430000000001</v>
+      </c>
+      <c r="G29">
+        <v>22.4</v>
+      </c>
+      <c r="H29">
+        <v>523.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>43.7</v>
+      </c>
+      <c r="K29">
+        <v>27.5</v>
+      </c>
+      <c r="L29">
+        <v>16.2</v>
+      </c>
+      <c r="M29">
+        <v>58.08642840000002</v>
+      </c>
+      <c r="N29">
+        <v>-41.88642840000001</v>
+      </c>
+      <c r="O29">
+        <v>-8.377285680000002</v>
+      </c>
+      <c r="P29">
+        <v>-33.50914272000001</v>
+      </c>
+      <c r="Q29">
+        <v>-6.00914272000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.110887019409473</v>
+      </c>
+      <c r="T29">
+        <v>1.010841170348111</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.05577895025131203</v>
+      </c>
+      <c r="W29">
+        <v>0.2254799866799867</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2788947512565603</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1438271205725117</v>
+      </c>
+      <c r="C30">
+        <v>200.4159270006238</v>
+      </c>
+      <c r="D30">
+        <v>430.2679270006239</v>
+      </c>
+      <c r="E30">
+        <v>-125.448</v>
+      </c>
+      <c r="F30">
+        <v>252.252</v>
+      </c>
+      <c r="G30">
+        <v>22.4</v>
+      </c>
+      <c r="H30">
+        <v>523.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>43.7</v>
+      </c>
+      <c r="K30">
+        <v>27.5</v>
+      </c>
+      <c r="L30">
+        <v>16.2</v>
+      </c>
+      <c r="M30">
+        <v>60.23777760000002</v>
+      </c>
+      <c r="N30">
+        <v>-44.03777760000001</v>
+      </c>
+      <c r="O30">
+        <v>-8.807555520000001</v>
+      </c>
+      <c r="P30">
+        <v>-35.23022208000001</v>
+      </c>
+      <c r="Q30">
+        <v>-7.730222080000008</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1118882280123823</v>
+      </c>
+      <c r="T30">
+        <v>1.024880631047391</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05378684488519374</v>
+      </c>
+      <c r="W30">
+        <v>0.2259557014414157</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2689342244259688</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1458271205725117</v>
+      </c>
+      <c r="C31">
+        <v>183.3665737761509</v>
+      </c>
+      <c r="D31">
+        <v>422.227573776151</v>
+      </c>
+      <c r="E31">
+        <v>-116.439</v>
+      </c>
+      <c r="F31">
+        <v>261.261</v>
+      </c>
+      <c r="G31">
+        <v>22.4</v>
+      </c>
+      <c r="H31">
+        <v>523.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>43.7</v>
+      </c>
+      <c r="K31">
+        <v>27.5</v>
+      </c>
+      <c r="L31">
+        <v>16.2</v>
+      </c>
+      <c r="M31">
+        <v>62.38912680000001</v>
+      </c>
+      <c r="N31">
+        <v>-46.18912680000001</v>
+      </c>
+      <c r="O31">
+        <v>-9.23782536</v>
+      </c>
+      <c r="P31">
+        <v>-36.95130144000001</v>
+      </c>
+      <c r="Q31">
+        <v>-9.451301440000005</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1129176396745285</v>
+      </c>
+      <c r="T31">
+        <v>1.039315569512847</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05193212609604914</v>
+      </c>
+      <c r="W31">
+        <v>0.2263986082882635</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2596606304802457</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1478271205725117</v>
+      </c>
+      <c r="C32">
+        <v>166.6122059895123</v>
+      </c>
+      <c r="D32">
+        <v>414.4822059895124</v>
+      </c>
+      <c r="E32">
+        <v>-107.4299999999999</v>
+      </c>
+      <c r="F32">
+        <v>270.27</v>
+      </c>
+      <c r="G32">
+        <v>22.4</v>
+      </c>
+      <c r="H32">
+        <v>523.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>43.7</v>
+      </c>
+      <c r="K32">
+        <v>27.5</v>
+      </c>
+      <c r="L32">
+        <v>16.2</v>
+      </c>
+      <c r="M32">
+        <v>64.54047600000001</v>
+      </c>
+      <c r="N32">
+        <v>-48.34047600000001</v>
+      </c>
+      <c r="O32">
+        <v>-9.6680952</v>
+      </c>
+      <c r="P32">
+        <v>-38.67238080000001</v>
+      </c>
+      <c r="Q32">
+        <v>-11.17238080000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1139764630984504</v>
+      </c>
+      <c r="T32">
+        <v>1.054162934791602</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05020105522618083</v>
+      </c>
+      <c r="W32">
+        <v>0.226811988011988</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2510052761309043</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1498271205725117</v>
+      </c>
+      <c r="C33">
+        <v>150.1368823768267</v>
+      </c>
+      <c r="D33">
+        <v>407.0158823768268</v>
+      </c>
+      <c r="E33">
+        <v>-98.42099999999994</v>
+      </c>
+      <c r="F33">
+        <v>279.2790000000001</v>
+      </c>
+      <c r="G33">
+        <v>22.4</v>
+      </c>
+      <c r="H33">
+        <v>523.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>43.7</v>
+      </c>
+      <c r="K33">
+        <v>27.5</v>
+      </c>
+      <c r="L33">
+        <v>16.2</v>
+      </c>
+      <c r="M33">
+        <v>66.69182520000001</v>
+      </c>
+      <c r="N33">
+        <v>-50.49182520000001</v>
+      </c>
+      <c r="O33">
+        <v>-10.09836504</v>
+      </c>
+      <c r="P33">
+        <v>-40.39346016000001</v>
+      </c>
+      <c r="Q33">
+        <v>-12.89346016000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1150659770563989</v>
+      </c>
+      <c r="T33">
+        <v>1.069440658484234</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.04858166634791693</v>
+      </c>
+      <c r="W33">
+        <v>0.2271986980761175</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2429083317395848</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1518271205725117</v>
+      </c>
+      <c r="C34">
+        <v>133.9257899884657</v>
+      </c>
+      <c r="D34">
+        <v>399.8137899884657</v>
+      </c>
+      <c r="E34">
+        <v>-89.41199999999998</v>
+      </c>
+      <c r="F34">
+        <v>288.288</v>
+      </c>
+      <c r="G34">
+        <v>22.4</v>
+      </c>
+      <c r="H34">
+        <v>523.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>43.7</v>
+      </c>
+      <c r="K34">
+        <v>27.5</v>
+      </c>
+      <c r="L34">
+        <v>16.2</v>
+      </c>
+      <c r="M34">
+        <v>68.84317440000001</v>
+      </c>
+      <c r="N34">
+        <v>-52.64317440000001</v>
+      </c>
+      <c r="O34">
+        <v>-10.52863488</v>
+      </c>
+      <c r="P34">
+        <v>-42.11453952000001</v>
+      </c>
+      <c r="Q34">
+        <v>-14.61453952</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1161875355425225</v>
+      </c>
+      <c r="T34">
+        <v>1.085167726991355</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.04706348927454453</v>
+      </c>
+      <c r="W34">
+        <v>0.2275612387612388</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2353174463727228</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1538271205725117</v>
+      </c>
+      <c r="C35">
+        <v>117.965146097903</v>
+      </c>
+      <c r="D35">
+        <v>392.8621460979031</v>
+      </c>
+      <c r="E35">
+        <v>-80.40299999999996</v>
+      </c>
+      <c r="F35">
+        <v>297.297</v>
+      </c>
+      <c r="G35">
+        <v>22.4</v>
+      </c>
+      <c r="H35">
+        <v>523.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>43.7</v>
+      </c>
+      <c r="K35">
+        <v>27.5</v>
+      </c>
+      <c r="L35">
+        <v>16.2</v>
+      </c>
+      <c r="M35">
+        <v>70.99452360000001</v>
+      </c>
+      <c r="N35">
+        <v>-54.79452360000001</v>
+      </c>
+      <c r="O35">
+        <v>-10.95890472</v>
+      </c>
+      <c r="P35">
+        <v>-43.83561888000001</v>
+      </c>
+      <c r="Q35">
+        <v>-16.33561888</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1173425733864407</v>
+      </c>
+      <c r="T35">
+        <v>1.101364260230032</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.04563732293289167</v>
+      </c>
+      <c r="W35">
+        <v>0.2279018072836255</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2281866146644584</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1558271205725117</v>
+      </c>
+      <c r="C36">
+        <v>102.242110168864</v>
+      </c>
+      <c r="D36">
+        <v>386.1481101688641</v>
+      </c>
+      <c r="E36">
+        <v>-71.39399999999995</v>
+      </c>
+      <c r="F36">
+        <v>306.306</v>
+      </c>
+      <c r="G36">
+        <v>22.4</v>
+      </c>
+      <c r="H36">
+        <v>523.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>43.7</v>
+      </c>
+      <c r="K36">
+        <v>27.5</v>
+      </c>
+      <c r="L36">
+        <v>16.2</v>
+      </c>
+      <c r="M36">
+        <v>73.14587280000001</v>
+      </c>
+      <c r="N36">
+        <v>-56.9458728</v>
+      </c>
+      <c r="O36">
+        <v>-11.38917456</v>
+      </c>
+      <c r="P36">
+        <v>-45.55669824</v>
+      </c>
+      <c r="Q36">
+        <v>-18.05669824</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1185326123771443</v>
+      </c>
+      <c r="T36">
+        <v>1.118051597506244</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04429504872898309</v>
+      </c>
+      <c r="W36">
+        <v>0.2282223423635188</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2214752436449156</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1578271205725117</v>
+      </c>
+      <c r="C37">
+        <v>86.74470469771552</v>
+      </c>
+      <c r="D37">
+        <v>379.6597046977156</v>
+      </c>
+      <c r="E37">
+        <v>-62.38499999999993</v>
+      </c>
+      <c r="F37">
+        <v>315.3150000000001</v>
+      </c>
+      <c r="G37">
+        <v>22.4</v>
+      </c>
+      <c r="H37">
+        <v>523.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>43.7</v>
+      </c>
+      <c r="K37">
+        <v>27.5</v>
+      </c>
+      <c r="L37">
+        <v>16.2</v>
+      </c>
+      <c r="M37">
+        <v>75.29722200000002</v>
+      </c>
+      <c r="N37">
+        <v>-59.09722200000002</v>
+      </c>
+      <c r="O37">
+        <v>-11.8194444</v>
+      </c>
+      <c r="P37">
+        <v>-47.27777760000001</v>
+      </c>
+      <c r="Q37">
+        <v>-19.77777760000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1197592679521773</v>
+      </c>
+      <c r="T37">
+        <v>1.135252391314033</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.043029475908155</v>
+      </c>
+      <c r="W37">
+        <v>0.2285245611531326</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2151473795407751</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1598271205725116</v>
+      </c>
+      <c r="C38">
+        <v>71.46174390443639</v>
+      </c>
+      <c r="D38">
+        <v>373.3857439044364</v>
+      </c>
+      <c r="E38">
+        <v>-53.37599999999998</v>
+      </c>
+      <c r="F38">
+        <v>324.324</v>
+      </c>
+      <c r="G38">
+        <v>22.4</v>
+      </c>
+      <c r="H38">
+        <v>523.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>43.7</v>
+      </c>
+      <c r="K38">
+        <v>27.5</v>
+      </c>
+      <c r="L38">
+        <v>16.2</v>
+      </c>
+      <c r="M38">
+        <v>77.4485712</v>
+      </c>
+      <c r="N38">
+        <v>-61.2485712</v>
+      </c>
+      <c r="O38">
+        <v>-12.24971424</v>
+      </c>
+      <c r="P38">
+        <v>-48.99885696</v>
+      </c>
+      <c r="Q38">
+        <v>-21.49885696</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1210242565139301</v>
+      </c>
+      <c r="T38">
+        <v>1.152990709928314</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04183421268848403</v>
+      </c>
+      <c r="W38">
+        <v>0.22880999000999</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2091710634424202</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1618271205725117</v>
+      </c>
+      <c r="C39">
+        <v>56.38276937903294</v>
+      </c>
+      <c r="D39">
+        <v>367.315769379033</v>
+      </c>
+      <c r="E39">
+        <v>-44.36699999999996</v>
+      </c>
+      <c r="F39">
+        <v>333.333</v>
+      </c>
+      <c r="G39">
+        <v>22.4</v>
+      </c>
+      <c r="H39">
+        <v>523.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>43.7</v>
+      </c>
+      <c r="K39">
+        <v>27.5</v>
+      </c>
+      <c r="L39">
+        <v>16.2</v>
+      </c>
+      <c r="M39">
+        <v>79.59992040000002</v>
+      </c>
+      <c r="N39">
+        <v>-63.39992040000001</v>
+      </c>
+      <c r="O39">
+        <v>-12.67998408</v>
+      </c>
+      <c r="P39">
+        <v>-50.71993632000002</v>
+      </c>
+      <c r="Q39">
+        <v>-23.21993632000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1223294034427226</v>
+      </c>
+      <c r="T39">
+        <v>1.171292149768446</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04070355829149797</v>
+      </c>
+      <c r="W39">
+        <v>0.2290799902799903</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2035177914574899</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1638271205725117</v>
+      </c>
+      <c r="C40">
+        <v>41.49799190456088</v>
+      </c>
+      <c r="D40">
+        <v>361.4399919045609</v>
+      </c>
+      <c r="E40">
+        <v>-35.35799999999995</v>
+      </c>
+      <c r="F40">
+        <v>342.342</v>
+      </c>
+      <c r="G40">
+        <v>22.4</v>
+      </c>
+      <c r="H40">
+        <v>523.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>43.7</v>
+      </c>
+      <c r="K40">
+        <v>27.5</v>
+      </c>
+      <c r="L40">
+        <v>16.2</v>
+      </c>
+      <c r="M40">
+        <v>81.75126960000001</v>
+      </c>
+      <c r="N40">
+        <v>-65.55126960000001</v>
+      </c>
+      <c r="O40">
+        <v>-13.11025392</v>
+      </c>
+      <c r="P40">
+        <v>-52.44101568000001</v>
+      </c>
+      <c r="Q40">
+        <v>-24.94101568000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1236766518853472</v>
+      </c>
+      <c r="T40">
+        <v>1.190183958635679</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.03963241202066908</v>
+      </c>
+      <c r="W40">
+        <v>0.2293357800094643</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1981620601033455</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1658271205725116</v>
+      </c>
+      <c r="C41">
+        <v>26.79823877600774</v>
+      </c>
+      <c r="D41">
+        <v>355.7492387760078</v>
+      </c>
+      <c r="E41">
+        <v>-26.34899999999993</v>
+      </c>
+      <c r="F41">
+        <v>351.3510000000001</v>
+      </c>
+      <c r="G41">
+        <v>22.4</v>
+      </c>
+      <c r="H41">
+        <v>523.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>43.7</v>
+      </c>
+      <c r="K41">
+        <v>27.5</v>
+      </c>
+      <c r="L41">
+        <v>16.2</v>
+      </c>
+      <c r="M41">
+        <v>83.90261880000001</v>
+      </c>
+      <c r="N41">
+        <v>-67.70261880000001</v>
+      </c>
+      <c r="O41">
+        <v>-13.54052376</v>
+      </c>
+      <c r="P41">
+        <v>-54.16209504000001</v>
+      </c>
+      <c r="Q41">
+        <v>-26.66209504000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1250680724080578</v>
+      </c>
+      <c r="T41">
+        <v>1.20969517107233</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.03861619632783141</v>
+      </c>
+      <c r="W41">
+        <v>0.2295784523169139</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1930809816391571</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1678271205725117</v>
+      </c>
+      <c r="C42">
+        <v>12.27490601871591</v>
+      </c>
+      <c r="D42">
+        <v>350.234906018716</v>
+      </c>
+      <c r="E42">
+        <v>-17.33999999999992</v>
+      </c>
+      <c r="F42">
+        <v>360.3600000000001</v>
+      </c>
+      <c r="G42">
+        <v>22.4</v>
+      </c>
+      <c r="H42">
+        <v>523.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>43.7</v>
+      </c>
+      <c r="K42">
+        <v>27.5</v>
+      </c>
+      <c r="L42">
+        <v>16.2</v>
+      </c>
+      <c r="M42">
+        <v>86.05396800000003</v>
+      </c>
+      <c r="N42">
+        <v>-69.85396800000002</v>
+      </c>
+      <c r="O42">
+        <v>-13.9707936</v>
+      </c>
+      <c r="P42">
+        <v>-55.88317440000002</v>
+      </c>
+      <c r="Q42">
+        <v>-28.38317440000002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1265058736148588</v>
+      </c>
+      <c r="T42">
+        <v>1.229856757256869</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.03765079141963562</v>
+      </c>
+      <c r="W42">
+        <v>0.229808991008991</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1882539570981782</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1698271205725117</v>
+      </c>
+      <c r="C43">
+        <v>-2.080085017161139</v>
+      </c>
+      <c r="D43">
+        <v>344.888914982839</v>
+      </c>
+      <c r="E43">
+        <v>-8.330999999999904</v>
+      </c>
+      <c r="F43">
+        <v>369.3690000000001</v>
+      </c>
+      <c r="G43">
+        <v>22.4</v>
+      </c>
+      <c r="H43">
+        <v>523.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>43.7</v>
+      </c>
+      <c r="K43">
+        <v>27.5</v>
+      </c>
+      <c r="L43">
+        <v>16.2</v>
+      </c>
+      <c r="M43">
+        <v>88.20531720000002</v>
+      </c>
+      <c r="N43">
+        <v>-72.00531720000002</v>
+      </c>
+      <c r="O43">
+        <v>-14.40106344</v>
+      </c>
+      <c r="P43">
+        <v>-57.60425376000002</v>
+      </c>
+      <c r="Q43">
+        <v>-30.10425376000002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1279924138456191</v>
+      </c>
+      <c r="T43">
+        <v>1.250701787040883</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03673247943379085</v>
+      </c>
+      <c r="W43">
+        <v>0.2300282839112107</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1836623971689543</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1718271205725117</v>
+      </c>
+      <c r="C44">
+        <v>-16.27432714671374</v>
+      </c>
+      <c r="D44">
+        <v>339.7036728532863</v>
+      </c>
+      <c r="E44">
+        <v>0.6780000000000541</v>
+      </c>
+      <c r="F44">
+        <v>378.378</v>
+      </c>
+      <c r="G44">
+        <v>22.4</v>
+      </c>
+      <c r="H44">
+        <v>523.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>43.7</v>
+      </c>
+      <c r="K44">
+        <v>27.5</v>
+      </c>
+      <c r="L44">
+        <v>16.2</v>
+      </c>
+      <c r="M44">
+        <v>90.35666640000001</v>
+      </c>
+      <c r="N44">
+        <v>-74.15666640000001</v>
+      </c>
+      <c r="O44">
+        <v>-14.83133328</v>
+      </c>
+      <c r="P44">
+        <v>-59.32533312000001</v>
+      </c>
+      <c r="Q44">
+        <v>-31.82533312000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1295302140843367</v>
+      </c>
+      <c r="T44">
+        <v>1.272265610955381</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03585789659012917</v>
+      </c>
+      <c r="W44">
+        <v>0.2302371342942772</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.179289482950646</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1738271205725117</v>
+      </c>
+      <c r="C45">
+        <v>-30.31496333080696</v>
+      </c>
+      <c r="D45">
+        <v>334.6720366691931</v>
+      </c>
+      <c r="E45">
+        <v>9.687000000000069</v>
+      </c>
+      <c r="F45">
+        <v>387.3870000000001</v>
+      </c>
+      <c r="G45">
+        <v>22.4</v>
+      </c>
+      <c r="H45">
+        <v>523.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>43.7</v>
+      </c>
+      <c r="K45">
+        <v>27.5</v>
+      </c>
+      <c r="L45">
+        <v>16.2</v>
+      </c>
+      <c r="M45">
+        <v>92.50801560000002</v>
+      </c>
+      <c r="N45">
+        <v>-76.30801560000002</v>
+      </c>
+      <c r="O45">
+        <v>-15.26160312</v>
+      </c>
+      <c r="P45">
+        <v>-61.04641248000001</v>
+      </c>
+      <c r="Q45">
+        <v>-33.54641248000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1311219722261671</v>
+      </c>
+      <c r="T45">
+        <v>1.294586060270388</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.0350239920182657</v>
+      </c>
+      <c r="W45">
+        <v>0.2304362707060382</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1751199600913286</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1758271205725117</v>
+      </c>
+      <c r="C46">
+        <v>-44.20871950565623</v>
+      </c>
+      <c r="D46">
+        <v>329.7872804943438</v>
+      </c>
+      <c r="E46">
+        <v>18.69600000000003</v>
+      </c>
+      <c r="F46">
+        <v>396.396</v>
+      </c>
+      <c r="G46">
+        <v>22.4</v>
+      </c>
+      <c r="H46">
+        <v>523.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>43.7</v>
+      </c>
+      <c r="K46">
+        <v>27.5</v>
+      </c>
+      <c r="L46">
+        <v>16.2</v>
+      </c>
+      <c r="M46">
+        <v>94.65936480000001</v>
+      </c>
+      <c r="N46">
+        <v>-78.4593648</v>
+      </c>
+      <c r="O46">
+        <v>-15.69187296</v>
+      </c>
+      <c r="P46">
+        <v>-62.76749184000001</v>
+      </c>
+      <c r="Q46">
+        <v>-35.26749184000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.132770578873063</v>
+      </c>
+      <c r="T46">
+        <v>1.317703668489502</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03422799219966875</v>
+      </c>
+      <c r="W46">
+        <v>0.2306263554627191</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1711399609983438</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1778271205725117</v>
+      </c>
+      <c r="C47">
+        <v>-57.96193457874813</v>
+      </c>
+      <c r="D47">
+        <v>325.0430654212519</v>
+      </c>
+      <c r="E47">
+        <v>27.70500000000004</v>
+      </c>
+      <c r="F47">
+        <v>405.405</v>
+      </c>
+      <c r="G47">
+        <v>22.4</v>
+      </c>
+      <c r="H47">
+        <v>523.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>43.7</v>
+      </c>
+      <c r="K47">
+        <v>27.5</v>
+      </c>
+      <c r="L47">
+        <v>16.2</v>
+      </c>
+      <c r="M47">
+        <v>96.81071400000002</v>
+      </c>
+      <c r="N47">
+        <v>-80.61071400000002</v>
+      </c>
+      <c r="O47">
+        <v>-16.1221428</v>
+      </c>
+      <c r="P47">
+        <v>-64.48857120000002</v>
+      </c>
+      <c r="Q47">
+        <v>-36.98857120000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1344791348525732</v>
+      </c>
+      <c r="T47">
+        <v>1.341661917007493</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03346737015078722</v>
+      </c>
+      <c r="W47">
+        <v>0.230807992007992</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1673368507539362</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1798271205725117</v>
+      </c>
+      <c r="C48">
+        <v>-71.58058787240844</v>
+      </c>
+      <c r="D48">
+        <v>320.4334121275916</v>
+      </c>
+      <c r="E48">
+        <v>36.71400000000006</v>
+      </c>
+      <c r="F48">
+        <v>414.414</v>
+      </c>
+      <c r="G48">
+        <v>22.4</v>
+      </c>
+      <c r="H48">
+        <v>523.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>43.7</v>
+      </c>
+      <c r="K48">
+        <v>27.5</v>
+      </c>
+      <c r="L48">
+        <v>16.2</v>
+      </c>
+      <c r="M48">
+        <v>98.96206320000002</v>
+      </c>
+      <c r="N48">
+        <v>-82.76206320000001</v>
+      </c>
+      <c r="O48">
+        <v>-16.55241264</v>
+      </c>
+      <c r="P48">
+        <v>-66.20965056000001</v>
+      </c>
+      <c r="Q48">
+        <v>-38.70965056000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1362509706831764</v>
+      </c>
+      <c r="T48">
+        <v>1.366507508063187</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03273981862577011</v>
+      </c>
+      <c r="W48">
+        <v>0.2309817313121661</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1636990931288506</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1818271205725117</v>
+      </c>
+      <c r="C49">
+        <v>-85.07032426484869</v>
+      </c>
+      <c r="D49">
+        <v>315.9526757351514</v>
+      </c>
+      <c r="E49">
+        <v>45.72300000000007</v>
+      </c>
+      <c r="F49">
+        <v>423.4230000000001</v>
+      </c>
+      <c r="G49">
+        <v>22.4</v>
+      </c>
+      <c r="H49">
+        <v>523.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>43.7</v>
+      </c>
+      <c r="K49">
+        <v>27.5</v>
+      </c>
+      <c r="L49">
+        <v>16.2</v>
+      </c>
+      <c r="M49">
+        <v>101.1134124</v>
+      </c>
+      <c r="N49">
+        <v>-84.91341240000001</v>
+      </c>
+      <c r="O49">
+        <v>-16.98268248</v>
+      </c>
+      <c r="P49">
+        <v>-67.93072992000002</v>
+      </c>
+      <c r="Q49">
+        <v>-40.43072992000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1380896682432363</v>
+      </c>
+      <c r="T49">
+        <v>1.392290668592681</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03204322674011543</v>
+      </c>
+      <c r="W49">
+        <v>0.2311480774544604</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1602161337005772</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1838271205725117</v>
+      </c>
+      <c r="C50">
+        <v>-98.43647725096446</v>
+      </c>
+      <c r="D50">
+        <v>311.5955227490356</v>
+      </c>
+      <c r="E50">
+        <v>54.73200000000003</v>
+      </c>
+      <c r="F50">
+        <v>432.432</v>
+      </c>
+      <c r="G50">
+        <v>22.4</v>
+      </c>
+      <c r="H50">
+        <v>523.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>43.7</v>
+      </c>
+      <c r="K50">
+        <v>27.5</v>
+      </c>
+      <c r="L50">
+        <v>16.2</v>
+      </c>
+      <c r="M50">
+        <v>103.2647616</v>
+      </c>
+      <c r="N50">
+        <v>-87.06476160000001</v>
+      </c>
+      <c r="O50">
+        <v>-17.41295232</v>
+      </c>
+      <c r="P50">
+        <v>-69.65180928000001</v>
+      </c>
+      <c r="Q50">
+        <v>-42.15180928000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1399990849402216</v>
+      </c>
+      <c r="T50">
+        <v>1.419065489142541</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03137565951636302</v>
+      </c>
+      <c r="W50">
+        <v>0.2313074925074925</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1568782975818152</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1858271205725117</v>
+      </c>
+      <c r="C51">
+        <v>-111.6840901209671</v>
+      </c>
+      <c r="D51">
+        <v>307.3569098790329</v>
+      </c>
+      <c r="E51">
+        <v>63.74100000000004</v>
+      </c>
+      <c r="F51">
+        <v>441.441</v>
+      </c>
+      <c r="G51">
+        <v>22.4</v>
+      </c>
+      <c r="H51">
+        <v>523.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>43.7</v>
+      </c>
+      <c r="K51">
+        <v>27.5</v>
+      </c>
+      <c r="L51">
+        <v>16.2</v>
+      </c>
+      <c r="M51">
+        <v>105.4161108</v>
+      </c>
+      <c r="N51">
+        <v>-89.21611080000001</v>
+      </c>
+      <c r="O51">
+        <v>-17.84322216</v>
+      </c>
+      <c r="P51">
+        <v>-71.37288864000001</v>
+      </c>
+      <c r="Q51">
+        <v>-43.87288864000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1419833807233633</v>
+      </c>
+      <c r="T51">
+        <v>1.44689030265514</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03073533993439643</v>
+      </c>
+      <c r="W51">
+        <v>0.2314604008236661</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1536766996719822</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1878271205725117</v>
+      </c>
+      <c r="C52">
+        <v>-124.8179354336629</v>
+      </c>
+      <c r="D52">
+        <v>303.2320645663372</v>
+      </c>
+      <c r="E52">
+        <v>72.75000000000006</v>
+      </c>
+      <c r="F52">
+        <v>450.45</v>
+      </c>
+      <c r="G52">
+        <v>22.4</v>
+      </c>
+      <c r="H52">
+        <v>523.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>43.7</v>
+      </c>
+      <c r="K52">
+        <v>27.5</v>
+      </c>
+      <c r="L52">
+        <v>16.2</v>
+      </c>
+      <c r="M52">
+        <v>107.56746</v>
+      </c>
+      <c r="N52">
+        <v>-91.36746000000001</v>
+      </c>
+      <c r="O52">
+        <v>-18.273492</v>
+      </c>
+      <c r="P52">
+        <v>-73.09396800000002</v>
+      </c>
+      <c r="Q52">
+        <v>-45.59396800000002</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1440470483378305</v>
+      </c>
+      <c r="T52">
+        <v>1.475828108708243</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0301206331357085</v>
+      </c>
+      <c r="W52">
+        <v>0.2316071928071928</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1506031656785426</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1898271205725117</v>
+      </c>
+      <c r="C53">
+        <v>-137.8425329424658</v>
+      </c>
+      <c r="D53">
+        <v>299.2164670575343</v>
+      </c>
+      <c r="E53">
+        <v>81.75900000000007</v>
+      </c>
+      <c r="F53">
+        <v>459.4590000000001</v>
+      </c>
+      <c r="G53">
+        <v>22.4</v>
+      </c>
+      <c r="H53">
+        <v>523.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>43.7</v>
+      </c>
+      <c r="K53">
+        <v>27.5</v>
+      </c>
+      <c r="L53">
+        <v>16.2</v>
+      </c>
+      <c r="M53">
+        <v>109.7188092</v>
+      </c>
+      <c r="N53">
+        <v>-93.51880920000002</v>
+      </c>
+      <c r="O53">
+        <v>-18.70376184</v>
+      </c>
+      <c r="P53">
+        <v>-74.81504736000002</v>
+      </c>
+      <c r="Q53">
+        <v>-47.31504736000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1461949472835005</v>
+      </c>
+      <c r="T53">
+        <v>1.505947049702288</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.02953003248598872</v>
+      </c>
+      <c r="W53">
+        <v>0.2317482282423459</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1476501624299437</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1918271205725117</v>
+      </c>
+      <c r="C54">
+        <v>-150.7621661156981</v>
+      </c>
+      <c r="D54">
+        <v>295.305833884302</v>
+      </c>
+      <c r="E54">
+        <v>90.76800000000009</v>
+      </c>
+      <c r="F54">
+        <v>468.4680000000001</v>
+      </c>
+      <c r="G54">
+        <v>22.4</v>
+      </c>
+      <c r="H54">
+        <v>523.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>43.7</v>
+      </c>
+      <c r="K54">
+        <v>27.5</v>
+      </c>
+      <c r="L54">
+        <v>16.2</v>
+      </c>
+      <c r="M54">
+        <v>111.8701584</v>
+      </c>
+      <c r="N54">
+        <v>-95.67015840000002</v>
+      </c>
+      <c r="O54">
+        <v>-19.13403168</v>
+      </c>
+      <c r="P54">
+        <v>-76.53612672000003</v>
+      </c>
+      <c r="Q54">
+        <v>-49.03612672000003</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1484323420185735</v>
+      </c>
+      <c r="T54">
+        <v>1.537320946571086</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02896214724587356</v>
+      </c>
+      <c r="W54">
+        <v>0.2318838392376854</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1448107362293678</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1938271205725117</v>
+      </c>
+      <c r="C55">
+        <v>-163.5808973781217</v>
+      </c>
+      <c r="D55">
+        <v>291.4961026218784</v>
+      </c>
+      <c r="E55">
+        <v>99.7770000000001</v>
+      </c>
+      <c r="F55">
+        <v>477.4770000000001</v>
+      </c>
+      <c r="G55">
+        <v>22.4</v>
+      </c>
+      <c r="H55">
+        <v>523.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>43.7</v>
+      </c>
+      <c r="K55">
+        <v>27.5</v>
+      </c>
+      <c r="L55">
+        <v>16.2</v>
+      </c>
+      <c r="M55">
+        <v>114.0215076</v>
+      </c>
+      <c r="N55">
+        <v>-97.82150760000002</v>
+      </c>
+      <c r="O55">
+        <v>-19.56430152</v>
+      </c>
+      <c r="P55">
+        <v>-78.25720608000002</v>
+      </c>
+      <c r="Q55">
+        <v>-50.75720608000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1507649450402452</v>
+      </c>
+      <c r="T55">
+        <v>1.570029902881109</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02841569163746085</v>
+      </c>
+      <c r="W55">
+        <v>0.2320143328369744</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1420784581873044</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1958271205725117</v>
+      </c>
+      <c r="C56">
+        <v>-176.3025821877152</v>
+      </c>
+      <c r="D56">
+        <v>287.7834178122849</v>
+      </c>
+      <c r="E56">
+        <v>108.7860000000001</v>
+      </c>
+      <c r="F56">
+        <v>486.4860000000001</v>
+      </c>
+      <c r="G56">
+        <v>22.4</v>
+      </c>
+      <c r="H56">
+        <v>523.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>43.7</v>
+      </c>
+      <c r="K56">
+        <v>27.5</v>
+      </c>
+      <c r="L56">
+        <v>16.2</v>
+      </c>
+      <c r="M56">
+        <v>116.1728568</v>
+      </c>
+      <c r="N56">
+        <v>-99.97285680000003</v>
+      </c>
+      <c r="O56">
+        <v>-19.99457136</v>
+      </c>
+      <c r="P56">
+        <v>-79.97828544000004</v>
+      </c>
+      <c r="Q56">
+        <v>-52.47828544000004</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1531989655845984</v>
+      </c>
+      <c r="T56">
+        <v>1.60416098772635</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02788947512565601</v>
+      </c>
+      <c r="W56">
+        <v>0.2321399933399934</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1394473756282801</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1978271205725117</v>
+      </c>
+      <c r="C57">
+        <v>-188.9308820502322</v>
+      </c>
+      <c r="D57">
+        <v>284.164117949768</v>
+      </c>
+      <c r="E57">
+        <v>117.7950000000001</v>
+      </c>
+      <c r="F57">
+        <v>495.4950000000001</v>
+      </c>
+      <c r="G57">
+        <v>22.4</v>
+      </c>
+      <c r="H57">
+        <v>523.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>43.7</v>
+      </c>
+      <c r="K57">
+        <v>27.5</v>
+      </c>
+      <c r="L57">
+        <v>16.2</v>
+      </c>
+      <c r="M57">
+        <v>118.324206</v>
+      </c>
+      <c r="N57">
+        <v>-102.124206</v>
+      </c>
+      <c r="O57">
+        <v>-20.4248412</v>
+      </c>
+      <c r="P57">
+        <v>-81.69936480000003</v>
+      </c>
+      <c r="Q57">
+        <v>-54.19936480000003</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1557411648198117</v>
+      </c>
+      <c r="T57">
+        <v>1.639809009675825</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.027382393759735</v>
+      </c>
+      <c r="W57">
+        <v>0.2322610843701753</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1369119687986751</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1998271205725117</v>
+      </c>
+      <c r="C58">
+        <v>-201.4692765638949</v>
+      </c>
+      <c r="D58">
+        <v>280.6347234361052</v>
+      </c>
+      <c r="E58">
+        <v>126.8040000000001</v>
+      </c>
+      <c r="F58">
+        <v>504.5040000000001</v>
+      </c>
+      <c r="G58">
+        <v>22.4</v>
+      </c>
+      <c r="H58">
+        <v>523.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>43.7</v>
+      </c>
+      <c r="K58">
+        <v>27.5</v>
+      </c>
+      <c r="L58">
+        <v>16.2</v>
+      </c>
+      <c r="M58">
+        <v>120.4755552</v>
+      </c>
+      <c r="N58">
+        <v>-104.2755552</v>
+      </c>
+      <c r="O58">
+        <v>-20.85511104</v>
+      </c>
+      <c r="P58">
+        <v>-83.42044416000003</v>
+      </c>
+      <c r="Q58">
+        <v>-55.92044416000003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1583989185657165</v>
+      </c>
+      <c r="T58">
+        <v>1.677077396259367</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02689342244259687</v>
+      </c>
+      <c r="W58">
+        <v>0.2323778507207079</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1344671122129845</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2018271205725117</v>
+      </c>
+      <c r="C59">
+        <v>-213.9210745775088</v>
+      </c>
+      <c r="D59">
+        <v>277.1919254224914</v>
+      </c>
+      <c r="E59">
+        <v>135.8130000000002</v>
+      </c>
+      <c r="F59">
+        <v>513.5130000000001</v>
+      </c>
+      <c r="G59">
+        <v>22.4</v>
+      </c>
+      <c r="H59">
+        <v>523.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>43.7</v>
+      </c>
+      <c r="K59">
+        <v>27.5</v>
+      </c>
+      <c r="L59">
+        <v>16.2</v>
+      </c>
+      <c r="M59">
+        <v>122.6269044</v>
+      </c>
+      <c r="N59">
+        <v>-106.4269044</v>
+      </c>
+      <c r="O59">
+        <v>-21.28538088</v>
+      </c>
+      <c r="P59">
+        <v>-85.14152352000004</v>
+      </c>
+      <c r="Q59">
+        <v>-57.64152352000004</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1611802887649192</v>
+      </c>
+      <c r="T59">
+        <v>1.716079196172375</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02642160801377938</v>
+      </c>
+      <c r="W59">
+        <v>0.2324905200063095</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.132108040068897</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2038271205725117</v>
+      </c>
+      <c r="C60">
+        <v>-226.2894245372105</v>
+      </c>
+      <c r="D60">
+        <v>273.8325754627896</v>
+      </c>
+      <c r="E60">
+        <v>144.8220000000001</v>
+      </c>
+      <c r="F60">
+        <v>522.522</v>
+      </c>
+      <c r="G60">
+        <v>22.4</v>
+      </c>
+      <c r="H60">
+        <v>523.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>43.7</v>
+      </c>
+      <c r="K60">
+        <v>27.5</v>
+      </c>
+      <c r="L60">
+        <v>16.2</v>
+      </c>
+      <c r="M60">
+        <v>124.7782536</v>
+      </c>
+      <c r="N60">
+        <v>-108.5782536</v>
+      </c>
+      <c r="O60">
+        <v>-21.71565072</v>
+      </c>
+      <c r="P60">
+        <v>-86.86260288000001</v>
+      </c>
+      <c r="Q60">
+        <v>-59.36260288000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.164094105164084</v>
+      </c>
+      <c r="T60">
+        <v>1.756938224652669</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02596606304802457</v>
+      </c>
+      <c r="W60">
+        <v>0.2325993041441318</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1298303152401229</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2058271205725117</v>
+      </c>
+      <c r="C61">
+        <v>-238.5773240898602</v>
+      </c>
+      <c r="D61">
+        <v>270.5536759101399</v>
+      </c>
+      <c r="E61">
+        <v>153.8310000000001</v>
+      </c>
+      <c r="F61">
+        <v>531.5310000000001</v>
+      </c>
+      <c r="G61">
+        <v>22.4</v>
+      </c>
+      <c r="H61">
+        <v>523.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>43.7</v>
+      </c>
+      <c r="K61">
+        <v>27.5</v>
+      </c>
+      <c r="L61">
+        <v>16.2</v>
+      </c>
+      <c r="M61">
+        <v>126.9296028</v>
+      </c>
+      <c r="N61">
+        <v>-110.7296028</v>
+      </c>
+      <c r="O61">
+        <v>-22.14592056</v>
+      </c>
+      <c r="P61">
+        <v>-88.58368224000003</v>
+      </c>
+      <c r="Q61">
+        <v>-61.08368224000003</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1671500589485738</v>
+      </c>
+      <c r="T61">
+        <v>1.799790376473466</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02552596028449873</v>
+      </c>
+      <c r="W61">
+        <v>0.2327044006840617</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1276298014224937</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2078271205725117</v>
+      </c>
+      <c r="C62">
+        <v>-250.7876290046426</v>
+      </c>
+      <c r="D62">
+        <v>267.3523709953575</v>
+      </c>
+      <c r="E62">
+        <v>162.8400000000001</v>
+      </c>
+      <c r="F62">
+        <v>540.5400000000001</v>
+      </c>
+      <c r="G62">
+        <v>22.4</v>
+      </c>
+      <c r="H62">
+        <v>523.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>43.7</v>
+      </c>
+      <c r="K62">
+        <v>27.5</v>
+      </c>
+      <c r="L62">
+        <v>16.2</v>
+      </c>
+      <c r="M62">
+        <v>129.080952</v>
+      </c>
+      <c r="N62">
+        <v>-112.880952</v>
+      </c>
+      <c r="O62">
+        <v>-22.5761904</v>
+      </c>
+      <c r="P62">
+        <v>-90.30476160000002</v>
+      </c>
+      <c r="Q62">
+        <v>-62.80476160000002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1703588104222881</v>
+      </c>
+      <c r="T62">
+        <v>1.844785135885303</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02510052761309042</v>
+      </c>
+      <c r="W62">
+        <v>0.232805994005994</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1255026380654521</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2098271205725117</v>
+      </c>
+      <c r="C63">
+        <v>-262.9230614686915</v>
+      </c>
+      <c r="D63">
+        <v>264.2259385313086</v>
+      </c>
+      <c r="E63">
+        <v>171.8490000000001</v>
+      </c>
+      <c r="F63">
+        <v>549.5490000000001</v>
+      </c>
+      <c r="G63">
+        <v>22.4</v>
+      </c>
+      <c r="H63">
+        <v>523.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>43.7</v>
+      </c>
+      <c r="K63">
+        <v>27.5</v>
+      </c>
+      <c r="L63">
+        <v>16.2</v>
+      </c>
+      <c r="M63">
+        <v>131.2323012</v>
+      </c>
+      <c r="N63">
+        <v>-115.0323012</v>
+      </c>
+      <c r="O63">
+        <v>-23.00646024</v>
+      </c>
+      <c r="P63">
+        <v>-92.02584096000002</v>
+      </c>
+      <c r="Q63">
+        <v>-64.52584096000002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1737321132536289</v>
+      </c>
+      <c r="T63">
+        <v>1.892087318856721</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02468904355385942</v>
+      </c>
+      <c r="W63">
+        <v>0.2329042563993384</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1234452177692972</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2118271205725117</v>
+      </c>
+      <c r="C64">
+        <v>-274.9862178073862</v>
+      </c>
+      <c r="D64">
+        <v>261.1717821926139</v>
+      </c>
+      <c r="E64">
+        <v>180.8580000000001</v>
+      </c>
+      <c r="F64">
+        <v>558.5580000000001</v>
+      </c>
+      <c r="G64">
+        <v>22.4</v>
+      </c>
+      <c r="H64">
+        <v>523.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>43.7</v>
+      </c>
+      <c r="K64">
+        <v>27.5</v>
+      </c>
+      <c r="L64">
+        <v>16.2</v>
+      </c>
+      <c r="M64">
+        <v>133.3836504</v>
+      </c>
+      <c r="N64">
+        <v>-117.1836504</v>
+      </c>
+      <c r="O64">
+        <v>-23.43673008</v>
+      </c>
+      <c r="P64">
+        <v>-93.74692032000002</v>
+      </c>
+      <c r="Q64">
+        <v>-66.24692032000002</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1772829583392507</v>
+      </c>
+      <c r="T64">
+        <v>1.941879090405582</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02429083317395847</v>
+      </c>
+      <c r="W64">
+        <v>0.2329993490380587</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1214541658697924</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2138271205725117</v>
+      </c>
+      <c r="C65">
+        <v>-286.9795756753362</v>
+      </c>
+      <c r="D65">
+        <v>258.1874243246639</v>
+      </c>
+      <c r="E65">
+        <v>189.867</v>
+      </c>
+      <c r="F65">
+        <v>567.567</v>
+      </c>
+      <c r="G65">
+        <v>22.4</v>
+      </c>
+      <c r="H65">
+        <v>523.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>43.7</v>
+      </c>
+      <c r="K65">
+        <v>27.5</v>
+      </c>
+      <c r="L65">
+        <v>16.2</v>
+      </c>
+      <c r="M65">
+        <v>135.5349996</v>
+      </c>
+      <c r="N65">
+        <v>-119.3349996</v>
+      </c>
+      <c r="O65">
+        <v>-23.86699992</v>
+      </c>
+      <c r="P65">
+        <v>-95.46799968000002</v>
+      </c>
+      <c r="Q65">
+        <v>-67.96799968000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1810257409970683</v>
+      </c>
+      <c r="T65">
+        <v>1.994362309065192</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02390526439341945</v>
+      </c>
+      <c r="W65">
+        <v>0.2330914228628514</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1195263219670972</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2158271205725117</v>
+      </c>
+      <c r="C66">
+        <v>-298.9055007599184</v>
+      </c>
+      <c r="D66">
+        <v>255.2704992400816</v>
+      </c>
+      <c r="E66">
+        <v>198.876</v>
+      </c>
+      <c r="F66">
+        <v>576.576</v>
+      </c>
+      <c r="G66">
+        <v>22.4</v>
+      </c>
+      <c r="H66">
+        <v>523.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>43.7</v>
+      </c>
+      <c r="K66">
+        <v>27.5</v>
+      </c>
+      <c r="L66">
+        <v>16.2</v>
+      </c>
+      <c r="M66">
+        <v>137.6863488</v>
+      </c>
+      <c r="N66">
+        <v>-121.4863488</v>
+      </c>
+      <c r="O66">
+        <v>-24.29726976</v>
+      </c>
+      <c r="P66">
+        <v>-97.18907904000002</v>
+      </c>
+      <c r="Q66">
+        <v>-69.68907904000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1849764560247646</v>
+      </c>
+      <c r="T66">
+        <v>2.049761262094781</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02353174463727226</v>
+      </c>
+      <c r="W66">
+        <v>0.2331806193806194</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1176587231863614</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2178271205725117</v>
+      </c>
+      <c r="C67">
+        <v>-310.7662530354815</v>
+      </c>
+      <c r="D67">
+        <v>252.4187469645186</v>
+      </c>
+      <c r="E67">
+        <v>207.885</v>
+      </c>
+      <c r="F67">
+        <v>585.585</v>
+      </c>
+      <c r="G67">
+        <v>22.4</v>
+      </c>
+      <c r="H67">
+        <v>523.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>43.7</v>
+      </c>
+      <c r="K67">
+        <v>27.5</v>
+      </c>
+      <c r="L67">
+        <v>16.2</v>
+      </c>
+      <c r="M67">
+        <v>139.837698</v>
+      </c>
+      <c r="N67">
+        <v>-123.637698</v>
+      </c>
+      <c r="O67">
+        <v>-24.7275396</v>
+      </c>
+      <c r="P67">
+        <v>-98.91015840000001</v>
+      </c>
+      <c r="Q67">
+        <v>-71.41015840000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1891529261969007</v>
+      </c>
+      <c r="T67">
+        <v>2.108325869583203</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02316971779669885</v>
+      </c>
+      <c r="W67">
+        <v>0.2332670713901483</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1158485889834943</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2198271205725117</v>
+      </c>
+      <c r="C68">
+        <v>-322.5639926029698</v>
+      </c>
+      <c r="D68">
+        <v>249.6300073970302</v>
+      </c>
+      <c r="E68">
+        <v>216.8940000000001</v>
+      </c>
+      <c r="F68">
+        <v>594.5940000000001</v>
+      </c>
+      <c r="G68">
+        <v>22.4</v>
+      </c>
+      <c r="H68">
+        <v>523.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>43.7</v>
+      </c>
+      <c r="K68">
+        <v>27.5</v>
+      </c>
+      <c r="L68">
+        <v>16.2</v>
+      </c>
+      <c r="M68">
+        <v>141.9890472</v>
+      </c>
+      <c r="N68">
+        <v>-125.7890472</v>
+      </c>
+      <c r="O68">
+        <v>-25.15780944</v>
+      </c>
+      <c r="P68">
+        <v>-100.63123776</v>
+      </c>
+      <c r="Q68">
+        <v>-73.13123776000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1935750710850449</v>
+      </c>
+      <c r="T68">
+        <v>2.17033545398271</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02281866146644583</v>
+      </c>
+      <c r="W68">
+        <v>0.2333509036418127</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1140933073322292</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2218271205725117</v>
+      </c>
+      <c r="C69">
+        <v>-334.3007851466779</v>
+      </c>
+      <c r="D69">
+        <v>246.9022148533221</v>
+      </c>
+      <c r="E69">
+        <v>225.9030000000001</v>
+      </c>
+      <c r="F69">
+        <v>603.6030000000001</v>
+      </c>
+      <c r="G69">
+        <v>22.4</v>
+      </c>
+      <c r="H69">
+        <v>523.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>43.7</v>
+      </c>
+      <c r="K69">
+        <v>27.5</v>
+      </c>
+      <c r="L69">
+        <v>16.2</v>
+      </c>
+      <c r="M69">
+        <v>144.1403964</v>
+      </c>
+      <c r="N69">
+        <v>-127.9403964</v>
+      </c>
+      <c r="O69">
+        <v>-25.58807928</v>
+      </c>
+      <c r="P69">
+        <v>-102.35231712</v>
+      </c>
+      <c r="Q69">
+        <v>-74.85231712000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1982652247542887</v>
+      </c>
+      <c r="T69">
+        <v>2.236103195012489</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02247808442963321</v>
+      </c>
+      <c r="W69">
+        <v>0.2334322334382036</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1123904221481661</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2238271205725117</v>
+      </c>
+      <c r="C70">
+        <v>-345.9786070371052</v>
+      </c>
+      <c r="D70">
+        <v>244.2333929628949</v>
+      </c>
+      <c r="E70">
+        <v>234.9120000000001</v>
+      </c>
+      <c r="F70">
+        <v>612.6120000000001</v>
+      </c>
+      <c r="G70">
+        <v>22.4</v>
+      </c>
+      <c r="H70">
+        <v>523.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>43.7</v>
+      </c>
+      <c r="K70">
+        <v>27.5</v>
+      </c>
+      <c r="L70">
+        <v>16.2</v>
+      </c>
+      <c r="M70">
+        <v>146.2917456</v>
+      </c>
+      <c r="N70">
+        <v>-130.0917456</v>
+      </c>
+      <c r="O70">
+        <v>-26.01834912</v>
+      </c>
+      <c r="P70">
+        <v>-104.07339648</v>
+      </c>
+      <c r="Q70">
+        <v>-76.57339648000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2032485130278602</v>
+      </c>
+      <c r="T70">
+        <v>2.305981419856629</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02214752436449155</v>
+      </c>
+      <c r="W70">
+        <v>0.2335111711817594</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1107376218224577</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2258271205725117</v>
+      </c>
+      <c r="C71">
+        <v>-357.599350106402</v>
+      </c>
+      <c r="D71">
+        <v>241.6216498935981</v>
+      </c>
+      <c r="E71">
+        <v>243.9210000000001</v>
+      </c>
+      <c r="F71">
+        <v>621.6210000000001</v>
+      </c>
+      <c r="G71">
+        <v>22.4</v>
+      </c>
+      <c r="H71">
+        <v>523.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>43.7</v>
+      </c>
+      <c r="K71">
+        <v>27.5</v>
+      </c>
+      <c r="L71">
+        <v>16.2</v>
+      </c>
+      <c r="M71">
+        <v>148.4430948</v>
+      </c>
+      <c r="N71">
+        <v>-132.2430948000001</v>
+      </c>
+      <c r="O71">
+        <v>-26.44861896</v>
+      </c>
+      <c r="P71">
+        <v>-105.79447584</v>
+      </c>
+      <c r="Q71">
+        <v>-78.29447584000005</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2085533037706944</v>
+      </c>
+      <c r="T71">
+        <v>2.380367917271359</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0218265457505134</v>
+      </c>
+      <c r="W71">
+        <v>0.2335878208747774</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.109132728752567</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2278271205725117</v>
+      </c>
+      <c r="C72">
+        <v>-369.1648261206564</v>
+      </c>
+      <c r="D72">
+        <v>239.0651738793438</v>
+      </c>
+      <c r="E72">
+        <v>252.9300000000001</v>
+      </c>
+      <c r="F72">
+        <v>630.6300000000001</v>
+      </c>
+      <c r="G72">
+        <v>22.4</v>
+      </c>
+      <c r="H72">
+        <v>523.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>43.7</v>
+      </c>
+      <c r="K72">
+        <v>27.5</v>
+      </c>
+      <c r="L72">
+        <v>16.2</v>
+      </c>
+      <c r="M72">
+        <v>150.594444</v>
+      </c>
+      <c r="N72">
+        <v>-134.394444</v>
+      </c>
+      <c r="O72">
+        <v>-26.87888880000001</v>
+      </c>
+      <c r="P72">
+        <v>-107.5155552000001</v>
+      </c>
+      <c r="Q72">
+        <v>-80.01555520000005</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2142117472297176</v>
+      </c>
+      <c r="T72">
+        <v>2.459713514513738</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0215147379540775</v>
+      </c>
+      <c r="W72">
+        <v>0.2336622805765663</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1075736897703874</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2298271205725117</v>
+      </c>
+      <c r="C73">
+        <v>-380.6767709712393</v>
+      </c>
+      <c r="D73">
+        <v>236.5622290287607</v>
+      </c>
+      <c r="E73">
+        <v>261.939</v>
+      </c>
+      <c r="F73">
+        <v>639.639</v>
+      </c>
+      <c r="G73">
+        <v>22.4</v>
+      </c>
+      <c r="H73">
+        <v>523.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>43.7</v>
+      </c>
+      <c r="K73">
+        <v>27.5</v>
+      </c>
+      <c r="L73">
+        <v>16.2</v>
+      </c>
+      <c r="M73">
+        <v>152.7457932</v>
+      </c>
+      <c r="N73">
+        <v>-136.5457932</v>
+      </c>
+      <c r="O73">
+        <v>-27.30915864</v>
+      </c>
+      <c r="P73">
+        <v>-109.23663456</v>
+      </c>
+      <c r="Q73">
+        <v>-81.73663456000003</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2202604281686733</v>
+      </c>
+      <c r="T73">
+        <v>2.544531221910763</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02121171347585106</v>
+      </c>
+      <c r="W73">
+        <v>0.2337346428219668</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1060585673792552</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2318271205725117</v>
+      </c>
+      <c r="C74">
+        <v>-392.1368486055855</v>
+      </c>
+      <c r="D74">
+        <v>234.1111513944145</v>
+      </c>
+      <c r="E74">
+        <v>270.948</v>
+      </c>
+      <c r="F74">
+        <v>648.648</v>
+      </c>
+      <c r="G74">
+        <v>22.4</v>
+      </c>
+      <c r="H74">
+        <v>523.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>43.7</v>
+      </c>
+      <c r="K74">
+        <v>27.5</v>
+      </c>
+      <c r="L74">
+        <v>16.2</v>
+      </c>
+      <c r="M74">
+        <v>154.8971424</v>
+      </c>
+      <c r="N74">
+        <v>-138.6971424</v>
+      </c>
+      <c r="O74">
+        <v>-27.73942848</v>
+      </c>
+      <c r="P74">
+        <v>-110.95771392</v>
+      </c>
+      <c r="Q74">
+        <v>-83.45771392000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2267411577461259</v>
+      </c>
+      <c r="T74">
+        <v>2.635407336979004</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02091710634424201</v>
+      </c>
+      <c r="W74">
+        <v>0.233804995004995</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.10458553172121</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2338271205725117</v>
+      </c>
+      <c r="C75">
+        <v>-403.5466547161118</v>
+      </c>
+      <c r="D75">
+        <v>231.7103452838882</v>
+      </c>
+      <c r="E75">
+        <v>279.9570000000001</v>
+      </c>
+      <c r="F75">
+        <v>657.657</v>
+      </c>
+      <c r="G75">
+        <v>22.4</v>
+      </c>
+      <c r="H75">
+        <v>523.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>43.7</v>
+      </c>
+      <c r="K75">
+        <v>27.5</v>
+      </c>
+      <c r="L75">
+        <v>16.2</v>
+      </c>
+      <c r="M75">
+        <v>157.0484916</v>
+      </c>
+      <c r="N75">
+        <v>-140.8484916</v>
+      </c>
+      <c r="O75">
+        <v>-28.16969832</v>
+      </c>
+      <c r="P75">
+        <v>-112.67879328</v>
+      </c>
+      <c r="Q75">
+        <v>-85.17879328000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2337019413663528</v>
+      </c>
+      <c r="T75">
+        <v>2.733015016126374</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02063057064089624</v>
+      </c>
+      <c r="W75">
+        <v>0.233873419730954</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1031528532044811</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2358271205725117</v>
+      </c>
+      <c r="C76">
+        <v>-414.9077202044629</v>
+      </c>
+      <c r="D76">
+        <v>229.3582797955372</v>
+      </c>
+      <c r="E76">
+        <v>288.9660000000001</v>
+      </c>
+      <c r="F76">
+        <v>666.6660000000001</v>
+      </c>
+      <c r="G76">
+        <v>22.4</v>
+      </c>
+      <c r="H76">
+        <v>523.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>43.7</v>
+      </c>
+      <c r="K76">
+        <v>27.5</v>
+      </c>
+      <c r="L76">
+        <v>16.2</v>
+      </c>
+      <c r="M76">
+        <v>159.1998408</v>
+      </c>
+      <c r="N76">
+        <v>-142.9998408</v>
+      </c>
+      <c r="O76">
+        <v>-28.59996816</v>
+      </c>
+      <c r="P76">
+        <v>-114.39987264</v>
+      </c>
+      <c r="Q76">
+        <v>-86.89987264000004</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2411981698804433</v>
+      </c>
+      <c r="T76">
+        <v>2.838130978285081</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02035177914574899</v>
+      </c>
+      <c r="W76">
+        <v>0.2339399951399951</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1017588957287449</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2378271205725117</v>
+      </c>
+      <c r="C77">
+        <v>-426.2215144368848</v>
+      </c>
+      <c r="D77">
+        <v>227.0534855631152</v>
+      </c>
+      <c r="E77">
+        <v>297.9750000000001</v>
+      </c>
+      <c r="F77">
+        <v>675.6750000000001</v>
+      </c>
+      <c r="G77">
+        <v>22.4</v>
+      </c>
+      <c r="H77">
+        <v>523.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>43.7</v>
+      </c>
+      <c r="K77">
+        <v>27.5</v>
+      </c>
+      <c r="L77">
+        <v>16.2</v>
+      </c>
+      <c r="M77">
+        <v>161.35119</v>
+      </c>
+      <c r="N77">
+        <v>-145.15119</v>
+      </c>
+      <c r="O77">
+        <v>-29.030238</v>
+      </c>
+      <c r="P77">
+        <v>-116.120952</v>
+      </c>
+      <c r="Q77">
+        <v>-88.62095200000005</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.249294096675661</v>
+      </c>
+      <c r="T77">
+        <v>2.951656217416485</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02008042209047233</v>
+      </c>
+      <c r="W77">
+        <v>0.2340047952047952</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1004021104523616</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2398271205725117</v>
+      </c>
+      <c r="C78">
+        <v>-437.4894483052751</v>
+      </c>
+      <c r="D78">
+        <v>224.7945516947249</v>
+      </c>
+      <c r="E78">
+        <v>306.9840000000001</v>
+      </c>
+      <c r="F78">
+        <v>684.6840000000001</v>
+      </c>
+      <c r="G78">
+        <v>22.4</v>
+      </c>
+      <c r="H78">
+        <v>523.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>43.7</v>
+      </c>
+      <c r="K78">
+        <v>27.5</v>
+      </c>
+      <c r="L78">
+        <v>16.2</v>
+      </c>
+      <c r="M78">
+        <v>163.5025392</v>
+      </c>
+      <c r="N78">
+        <v>-147.3025392</v>
+      </c>
+      <c r="O78">
+        <v>-29.46050784</v>
+      </c>
+      <c r="P78">
+        <v>-117.84203136</v>
+      </c>
+      <c r="Q78">
+        <v>-90.34203136000004</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2580646840371469</v>
+      </c>
+      <c r="T78">
+        <v>3.074641893142172</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.01981620601033454</v>
+      </c>
+      <c r="W78">
+        <v>0.2340678900047321</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.09908103005167268</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2418271205725117</v>
+      </c>
+      <c r="C79">
+        <v>-448.7128771073074</v>
+      </c>
+      <c r="D79">
+        <v>222.5801228926927</v>
+      </c>
+      <c r="E79">
+        <v>315.9930000000001</v>
+      </c>
+      <c r="F79">
+        <v>693.6930000000001</v>
+      </c>
+      <c r="G79">
+        <v>22.4</v>
+      </c>
+      <c r="H79">
+        <v>523.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>43.7</v>
+      </c>
+      <c r="K79">
+        <v>27.5</v>
+      </c>
+      <c r="L79">
+        <v>16.2</v>
+      </c>
+      <c r="M79">
+        <v>165.6538884</v>
+      </c>
+      <c r="N79">
+        <v>-149.4538884</v>
+      </c>
+      <c r="O79">
+        <v>-29.89077768</v>
+      </c>
+      <c r="P79">
+        <v>-119.56311072</v>
+      </c>
+      <c r="Q79">
+        <v>-92.06311072000004</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2675979311691967</v>
+      </c>
+      <c r="T79">
+        <v>3.208321975452701</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.019558852685525</v>
+      </c>
+      <c r="W79">
+        <v>0.2341293459786966</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.09779426342762498</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2438271205725117</v>
+      </c>
+      <c r="C80">
+        <v>-459.893103257986</v>
+      </c>
+      <c r="D80">
+        <v>220.4088967420141</v>
+      </c>
+      <c r="E80">
+        <v>325.0020000000001</v>
+      </c>
+      <c r="F80">
+        <v>702.7020000000001</v>
+      </c>
+      <c r="G80">
+        <v>22.4</v>
+      </c>
+      <c r="H80">
+        <v>523.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>43.7</v>
+      </c>
+      <c r="K80">
+        <v>27.5</v>
+      </c>
+      <c r="L80">
+        <v>16.2</v>
+      </c>
+      <c r="M80">
+        <v>167.8052376</v>
+      </c>
+      <c r="N80">
+        <v>-151.6052376</v>
+      </c>
+      <c r="O80">
+        <v>-30.32104752</v>
+      </c>
+      <c r="P80">
+        <v>-121.28419008</v>
+      </c>
+      <c r="Q80">
+        <v>-93.78419008000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.277997837131433</v>
+      </c>
+      <c r="T80">
+        <v>3.354154792518733</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01930809816391571</v>
+      </c>
+      <c r="W80">
+        <v>0.2341892261584569</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.09654049081957849</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2458271205725117</v>
+      </c>
+      <c r="C81">
+        <v>-471.0313788440301</v>
+      </c>
+      <c r="D81">
+        <v>218.2796211559701</v>
+      </c>
+      <c r="E81">
+        <v>334.0110000000001</v>
+      </c>
+      <c r="F81">
+        <v>711.7110000000001</v>
+      </c>
+      <c r="G81">
+        <v>22.4</v>
+      </c>
+      <c r="H81">
+        <v>523.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>43.7</v>
+      </c>
+      <c r="K81">
+        <v>27.5</v>
+      </c>
+      <c r="L81">
+        <v>16.2</v>
+      </c>
+      <c r="M81">
+        <v>169.9565868</v>
+      </c>
+      <c r="N81">
+        <v>-153.7565868</v>
+      </c>
+      <c r="O81">
+        <v>-30.75131736</v>
+      </c>
+      <c r="P81">
+        <v>-123.00526944</v>
+      </c>
+      <c r="Q81">
+        <v>-95.50526944000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2893882103281679</v>
+      </c>
+      <c r="T81">
+        <v>3.513876449305339</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01906369185804335</v>
+      </c>
+      <c r="W81">
+        <v>0.2342475903842993</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.09531845929021676</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2478271205725117</v>
+      </c>
+      <c r="C82">
+        <v>-482.1289080316122</v>
+      </c>
+      <c r="D82">
+        <v>216.1910919683879</v>
+      </c>
+      <c r="E82">
+        <v>343.0200000000002</v>
+      </c>
+      <c r="F82">
+        <v>720.7200000000001</v>
+      </c>
+      <c r="G82">
+        <v>22.4</v>
+      </c>
+      <c r="H82">
+        <v>523.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>43.7</v>
+      </c>
+      <c r="K82">
+        <v>27.5</v>
+      </c>
+      <c r="L82">
+        <v>16.2</v>
+      </c>
+      <c r="M82">
+        <v>172.1079360000001</v>
+      </c>
+      <c r="N82">
+        <v>-155.9079360000001</v>
+      </c>
+      <c r="O82">
+        <v>-31.18158720000001</v>
+      </c>
+      <c r="P82">
+        <v>-124.7263488000001</v>
+      </c>
+      <c r="Q82">
+        <v>-97.22634880000005</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3019176208445764</v>
+      </c>
+      <c r="T82">
+        <v>3.689570271770607</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01882539570981781</v>
+      </c>
+      <c r="W82">
+        <v>0.2343044955044955</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.09412697854908902</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2498271205725117</v>
+      </c>
+      <c r="C83">
+        <v>-493.1868493371835</v>
+      </c>
+      <c r="D83">
+        <v>214.1421506628167</v>
+      </c>
+      <c r="E83">
+        <v>352.0290000000002</v>
+      </c>
+      <c r="F83">
+        <v>729.7290000000002</v>
+      </c>
+      <c r="G83">
+        <v>22.4</v>
+      </c>
+      <c r="H83">
+        <v>523.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>43.7</v>
+      </c>
+      <c r="K83">
+        <v>27.5</v>
+      </c>
+      <c r="L83">
+        <v>16.2</v>
+      </c>
+      <c r="M83">
+        <v>174.2592852000001</v>
+      </c>
+      <c r="N83">
+        <v>-158.0592852000001</v>
+      </c>
+      <c r="O83">
+        <v>-31.61185704</v>
+      </c>
+      <c r="P83">
+        <v>-126.4474281600001</v>
+      </c>
+      <c r="Q83">
+        <v>-98.94742816000006</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3157659166785014</v>
+      </c>
+      <c r="T83">
+        <v>3.883758180811165</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01859298341710401</v>
+      </c>
+      <c r="W83">
+        <v>0.2343599955599956</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.09296491708552002</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2518271205725117</v>
+      </c>
+      <c r="C84">
+        <v>-504.2063177703792</v>
+      </c>
+      <c r="D84">
+        <v>212.1316822296209</v>
+      </c>
+      <c r="E84">
+        <v>361.0380000000002</v>
+      </c>
+      <c r="F84">
+        <v>738.7380000000002</v>
+      </c>
+      <c r="G84">
+        <v>22.4</v>
+      </c>
+      <c r="H84">
+        <v>523.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>43.7</v>
+      </c>
+      <c r="K84">
+        <v>27.5</v>
+      </c>
+      <c r="L84">
+        <v>16.2</v>
+      </c>
+      <c r="M84">
+        <v>176.4106344</v>
+      </c>
+      <c r="N84">
+        <v>-160.2106344000001</v>
+      </c>
+      <c r="O84">
+        <v>-32.04212688</v>
+      </c>
+      <c r="P84">
+        <v>-128.16850752</v>
+      </c>
+      <c r="Q84">
+        <v>-100.66850752</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3311529120495293</v>
+      </c>
+      <c r="T84">
+        <v>4.099522524189564</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01836623971689542</v>
+      </c>
+      <c r="W84">
+        <v>0.2344141419556054</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.09183119858447708</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2538271205725117</v>
+      </c>
+      <c r="C85">
+        <v>-515.1883868573374</v>
+      </c>
+      <c r="D85">
+        <v>210.1586131426628</v>
+      </c>
+      <c r="E85">
+        <v>370.0470000000002</v>
+      </c>
+      <c r="F85">
+        <v>747.7470000000002</v>
+      </c>
+      <c r="G85">
+        <v>22.4</v>
+      </c>
+      <c r="H85">
+        <v>523.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>43.7</v>
+      </c>
+      <c r="K85">
+        <v>27.5</v>
+      </c>
+      <c r="L85">
+        <v>16.2</v>
+      </c>
+      <c r="M85">
+        <v>178.5619836</v>
+      </c>
+      <c r="N85">
+        <v>-162.3619836000001</v>
+      </c>
+      <c r="O85">
+        <v>-32.47239672000001</v>
+      </c>
+      <c r="P85">
+        <v>-129.8895868800001</v>
+      </c>
+      <c r="Q85">
+        <v>-102.3895868800001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3483501421700899</v>
+      </c>
+      <c r="T85">
+        <v>4.34067090796542</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01814495972030632</v>
+      </c>
+      <c r="W85">
+        <v>0.2344669836187909</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.0907247986015316</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2558271205725117</v>
+      </c>
+      <c r="C86">
+        <v>-526.1340905521407</v>
+      </c>
+      <c r="D86">
+        <v>208.2219094478594</v>
+      </c>
+      <c r="E86">
+        <v>379.0560000000001</v>
+      </c>
+      <c r="F86">
+        <v>756.7560000000001</v>
+      </c>
+      <c r="G86">
+        <v>22.4</v>
+      </c>
+      <c r="H86">
+        <v>523.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>43.7</v>
+      </c>
+      <c r="K86">
+        <v>27.5</v>
+      </c>
+      <c r="L86">
+        <v>16.2</v>
+      </c>
+      <c r="M86">
+        <v>180.7133328</v>
+      </c>
+      <c r="N86">
+        <v>-164.5133328</v>
+      </c>
+      <c r="O86">
+        <v>-32.90266656</v>
+      </c>
+      <c r="P86">
+        <v>-131.61066624</v>
+      </c>
+      <c r="Q86">
+        <v>-104.11066624</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3676970260557204</v>
+      </c>
+      <c r="T86">
+        <v>4.611962839713257</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01792894829506458</v>
+      </c>
+      <c r="W86">
+        <v>0.2345185671471386</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.08964474147532286</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2578271205725117</v>
+      </c>
+      <c r="C87">
+        <v>-537.044425043537</v>
+      </c>
+      <c r="D87">
+        <v>206.3205749564631</v>
+      </c>
+      <c r="E87">
+        <v>388.0650000000001</v>
+      </c>
+      <c r="F87">
+        <v>765.7650000000001</v>
+      </c>
+      <c r="G87">
+        <v>22.4</v>
+      </c>
+      <c r="H87">
+        <v>523.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>43.7</v>
+      </c>
+      <c r="K87">
+        <v>27.5</v>
+      </c>
+      <c r="L87">
+        <v>16.2</v>
+      </c>
+      <c r="M87">
+        <v>182.864682</v>
+      </c>
+      <c r="N87">
+        <v>-166.6646820000001</v>
+      </c>
+      <c r="O87">
+        <v>-33.3329364</v>
+      </c>
+      <c r="P87">
+        <v>-133.3317456000001</v>
+      </c>
+      <c r="Q87">
+        <v>-105.8317456000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3896234944594351</v>
+      </c>
+      <c r="T87">
+        <v>4.919427029027474</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01771801949159323</v>
+      </c>
+      <c r="W87">
+        <v>0.2345689369454075</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.08859009745796609</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2598271205725117</v>
+      </c>
+      <c r="C88">
+        <v>-547.9203504635673</v>
+      </c>
+      <c r="D88">
+        <v>204.4536495364328</v>
+      </c>
+      <c r="E88">
+        <v>397.0740000000001</v>
+      </c>
+      <c r="F88">
+        <v>774.7740000000001</v>
+      </c>
+      <c r="G88">
+        <v>22.4</v>
+      </c>
+      <c r="H88">
+        <v>523.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>43.7</v>
+      </c>
+      <c r="K88">
+        <v>27.5</v>
+      </c>
+      <c r="L88">
+        <v>16.2</v>
+      </c>
+      <c r="M88">
+        <v>185.0160312</v>
+      </c>
+      <c r="N88">
+        <v>-168.8160312000001</v>
+      </c>
+      <c r="O88">
+        <v>-33.76320624</v>
+      </c>
+      <c r="P88">
+        <v>-135.0528249600001</v>
+      </c>
+      <c r="Q88">
+        <v>-107.5528249600001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4146823154922518</v>
+      </c>
+      <c r="T88">
+        <v>5.270814673958008</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01751199600913285</v>
+      </c>
+      <c r="W88">
+        <v>0.2346181353530191</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.08755998004566423</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2618271205725117</v>
+      </c>
+      <c r="C89">
+        <v>-558.7627925042626</v>
+      </c>
+      <c r="D89">
+        <v>202.6202074957375</v>
+      </c>
+      <c r="E89">
+        <v>406.0830000000001</v>
+      </c>
+      <c r="F89">
+        <v>783.7830000000001</v>
+      </c>
+      <c r="G89">
+        <v>22.4</v>
+      </c>
+      <c r="H89">
+        <v>523.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>43.7</v>
+      </c>
+      <c r="K89">
+        <v>27.5</v>
+      </c>
+      <c r="L89">
+        <v>16.2</v>
+      </c>
+      <c r="M89">
+        <v>187.1673804</v>
+      </c>
+      <c r="N89">
+        <v>-170.9673804000001</v>
+      </c>
+      <c r="O89">
+        <v>-34.19347608</v>
+      </c>
+      <c r="P89">
+        <v>-136.77390432</v>
+      </c>
+      <c r="Q89">
+        <v>-109.27390432</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4435963397608866</v>
+      </c>
+      <c r="T89">
+        <v>5.676261956570163</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01731070869868305</v>
+      </c>
+      <c r="W89">
+        <v>0.2346662027627545</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.08655354349341515</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2638271205725117</v>
+      </c>
+      <c r="C90">
+        <v>-569.5726439481261</v>
+      </c>
+      <c r="D90">
+        <v>200.8193560518739</v>
+      </c>
+      <c r="E90">
+        <v>415.092</v>
+      </c>
+      <c r="F90">
+        <v>792.792</v>
+      </c>
+      <c r="G90">
+        <v>22.4</v>
+      </c>
+      <c r="H90">
+        <v>523.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>43.7</v>
+      </c>
+      <c r="K90">
+        <v>27.5</v>
+      </c>
+      <c r="L90">
+        <v>16.2</v>
+      </c>
+      <c r="M90">
+        <v>189.3187296</v>
+      </c>
+      <c r="N90">
+        <v>-173.1187296</v>
+      </c>
+      <c r="O90">
+        <v>-34.62374592</v>
+      </c>
+      <c r="P90">
+        <v>-138.49498368</v>
+      </c>
+      <c r="Q90">
+        <v>-110.99498368</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4773293680742939</v>
+      </c>
+      <c r="T90">
+        <v>6.149283786284344</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01711399609983438</v>
+      </c>
+      <c r="W90">
+        <v>0.2347131777313596</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.08556998049917186</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2658271205725117</v>
+      </c>
+      <c r="C91">
+        <v>-580.3507661177194</v>
+      </c>
+      <c r="D91">
+        <v>199.0502338822806</v>
+      </c>
+      <c r="E91">
+        <v>424.1010000000001</v>
+      </c>
+      <c r="F91">
+        <v>801.801</v>
+      </c>
+      <c r="G91">
+        <v>22.4</v>
+      </c>
+      <c r="H91">
+        <v>523.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>43.7</v>
+      </c>
+      <c r="K91">
+        <v>27.5</v>
+      </c>
+      <c r="L91">
+        <v>16.2</v>
+      </c>
+      <c r="M91">
+        <v>191.4700788</v>
+      </c>
+      <c r="N91">
+        <v>-175.2700788</v>
+      </c>
+      <c r="O91">
+        <v>-35.05401576</v>
+      </c>
+      <c r="P91">
+        <v>-140.21606304</v>
+      </c>
+      <c r="Q91">
+        <v>-112.71606304</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5171956742628661</v>
+      </c>
+      <c r="T91">
+        <v>6.708309585037466</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.016921704008825</v>
+      </c>
+      <c r="W91">
+        <v>0.2347590970826926</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.084608520044125</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2678271205725117</v>
+      </c>
+      <c r="C92">
+        <v>-591.0979902492957</v>
+      </c>
+      <c r="D92">
+        <v>197.3120097507044</v>
+      </c>
+      <c r="E92">
+        <v>433.1100000000001</v>
+      </c>
+      <c r="F92">
+        <v>810.8100000000001</v>
+      </c>
+      <c r="G92">
+        <v>22.4</v>
+      </c>
+      <c r="H92">
+        <v>523.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>43.7</v>
+      </c>
+      <c r="K92">
+        <v>27.5</v>
+      </c>
+      <c r="L92">
+        <v>16.2</v>
+      </c>
+      <c r="M92">
+        <v>193.621428</v>
+      </c>
+      <c r="N92">
+        <v>-177.421428</v>
+      </c>
+      <c r="O92">
+        <v>-35.4842856</v>
+      </c>
+      <c r="P92">
+        <v>-141.9371424000001</v>
+      </c>
+      <c r="Q92">
+        <v>-114.4371424000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5650352416891526</v>
+      </c>
+      <c r="T92">
+        <v>7.379140543541213</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01673368507539361</v>
+      </c>
+      <c r="W92">
+        <v>0.234803996003996</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.08366842537696806</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2698271205725117</v>
+      </c>
+      <c r="C93">
+        <v>-601.8151187950849</v>
+      </c>
+      <c r="D93">
+        <v>195.6038812049151</v>
+      </c>
+      <c r="E93">
+        <v>442.1190000000001</v>
+      </c>
+      <c r="F93">
+        <v>819.8190000000001</v>
+      </c>
+      <c r="G93">
+        <v>22.4</v>
+      </c>
+      <c r="H93">
+        <v>523.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>43.7</v>
+      </c>
+      <c r="K93">
+        <v>27.5</v>
+      </c>
+      <c r="L93">
+        <v>16.2</v>
+      </c>
+      <c r="M93">
+        <v>195.7727772</v>
+      </c>
+      <c r="N93">
+        <v>-179.5727772</v>
+      </c>
+      <c r="O93">
+        <v>-35.91455544</v>
+      </c>
+      <c r="P93">
+        <v>-143.6582217600001</v>
+      </c>
+      <c r="Q93">
+        <v>-116.1582217600001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6235058240990585</v>
+      </c>
+      <c r="T93">
+        <v>8.199045048379126</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01654979842621346</v>
+      </c>
+      <c r="W93">
+        <v>0.2348479081358202</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.08274899213106723</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2718271205725117</v>
+      </c>
+      <c r="C94">
+        <v>-612.502926658516</v>
+      </c>
+      <c r="D94">
+        <v>193.9250733414841</v>
+      </c>
+      <c r="E94">
+        <v>451.1280000000001</v>
+      </c>
+      <c r="F94">
+        <v>828.8280000000001</v>
+      </c>
+      <c r="G94">
+        <v>22.4</v>
+      </c>
+      <c r="H94">
+        <v>523.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>43.7</v>
+      </c>
+      <c r="K94">
+        <v>27.5</v>
+      </c>
+      <c r="L94">
+        <v>16.2</v>
+      </c>
+      <c r="M94">
+        <v>197.9241264</v>
+      </c>
+      <c r="N94">
+        <v>-181.7241264</v>
+      </c>
+      <c r="O94">
+        <v>-36.34482528</v>
+      </c>
+      <c r="P94">
+        <v>-145.37930112</v>
+      </c>
+      <c r="Q94">
+        <v>-117.87930112</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6965940521114411</v>
+      </c>
+      <c r="T94">
+        <v>9.22392567942652</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01636990931288506</v>
+      </c>
+      <c r="W94">
+        <v>0.2348908656560831</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.08184954656442522</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2738271205725117</v>
+      </c>
+      <c r="C95">
+        <v>-623.1621623663705</v>
+      </c>
+      <c r="D95">
+        <v>192.2748376336296</v>
+      </c>
+      <c r="E95">
+        <v>460.1370000000001</v>
+      </c>
+      <c r="F95">
+        <v>837.8370000000001</v>
+      </c>
+      <c r="G95">
+        <v>22.4</v>
+      </c>
+      <c r="H95">
+        <v>523.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>43.7</v>
+      </c>
+      <c r="K95">
+        <v>27.5</v>
+      </c>
+      <c r="L95">
+        <v>16.2</v>
+      </c>
+      <c r="M95">
+        <v>200.0754756</v>
+      </c>
+      <c r="N95">
+        <v>-183.8754756</v>
+      </c>
+      <c r="O95">
+        <v>-36.77509512</v>
+      </c>
+      <c r="P95">
+        <v>-147.10038048</v>
+      </c>
+      <c r="Q95">
+        <v>-119.60038048</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7905646309845042</v>
+      </c>
+      <c r="T95">
+        <v>10.54162934791603</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01619388878263898</v>
+      </c>
+      <c r="W95">
+        <v>0.2349328993587058</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.08096944391319483</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2758271205725117</v>
+      </c>
+      <c r="C96">
+        <v>-633.793549181594</v>
+      </c>
+      <c r="D96">
+        <v>190.652450818406</v>
+      </c>
+      <c r="E96">
+        <v>469.1460000000001</v>
+      </c>
+      <c r="F96">
+        <v>846.8460000000001</v>
+      </c>
+      <c r="G96">
+        <v>22.4</v>
+      </c>
+      <c r="H96">
+        <v>523.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>43.7</v>
+      </c>
+      <c r="K96">
+        <v>27.5</v>
+      </c>
+      <c r="L96">
+        <v>16.2</v>
+      </c>
+      <c r="M96">
+        <v>202.2268248</v>
+      </c>
+      <c r="N96">
+        <v>-186.0268248</v>
+      </c>
+      <c r="O96">
+        <v>-37.20536496</v>
+      </c>
+      <c r="P96">
+        <v>-148.82145984</v>
+      </c>
+      <c r="Q96">
+        <v>-121.32145984</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9158587361485886</v>
+      </c>
+      <c r="T96">
+        <v>12.2985675725687</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01602161337005771</v>
+      </c>
+      <c r="W96">
+        <v>0.2349740387272302</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.08010806685028848</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2778271205725117</v>
+      </c>
+      <c r="C97">
+        <v>-644.3977861602411</v>
+      </c>
+      <c r="D97">
+        <v>189.057213839759</v>
+      </c>
+      <c r="E97">
+        <v>478.1550000000001</v>
+      </c>
+      <c r="F97">
+        <v>855.8550000000001</v>
+      </c>
+      <c r="G97">
+        <v>22.4</v>
+      </c>
+      <c r="H97">
+        <v>523.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>43.7</v>
+      </c>
+      <c r="K97">
+        <v>27.5</v>
+      </c>
+      <c r="L97">
+        <v>16.2</v>
+      </c>
+      <c r="M97">
+        <v>204.378174</v>
+      </c>
+      <c r="N97">
+        <v>-188.178174</v>
+      </c>
+      <c r="O97">
+        <v>-37.6356348</v>
+      </c>
+      <c r="P97">
+        <v>-150.5425392</v>
+      </c>
+      <c r="Q97">
+        <v>-123.0425392</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.091270483378307</v>
+      </c>
+      <c r="T97">
+        <v>14.75828108708244</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01585296480826763</v>
+      </c>
+      <c r="W97">
+        <v>0.2350143120037857</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.07926482404133817</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2798271205725117</v>
+      </c>
+      <c r="C98">
+        <v>-654.9755491557969</v>
+      </c>
+      <c r="D98">
+        <v>187.4884508442031</v>
+      </c>
+      <c r="E98">
+        <v>487.164</v>
+      </c>
+      <c r="F98">
+        <v>864.864</v>
+      </c>
+      <c r="G98">
+        <v>22.4</v>
+      </c>
+      <c r="H98">
+        <v>523.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>43.7</v>
+      </c>
+      <c r="K98">
+        <v>27.5</v>
+      </c>
+      <c r="L98">
+        <v>16.2</v>
+      </c>
+      <c r="M98">
+        <v>206.5295232</v>
+      </c>
+      <c r="N98">
+        <v>-190.3295232</v>
+      </c>
+      <c r="O98">
+        <v>-38.06590464</v>
+      </c>
+      <c r="P98">
+        <v>-152.2636185600001</v>
+      </c>
+      <c r="Q98">
+        <v>-124.7636185600001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.35438810422288</v>
+      </c>
+      <c r="T98">
+        <v>18.44785135885301</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01568782975818151</v>
+      </c>
+      <c r="W98">
+        <v>0.2350537462537463</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.07843914879090752</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2818271205725117</v>
+      </c>
+      <c r="C99">
+        <v>-665.5274917739091</v>
+      </c>
+      <c r="D99">
+        <v>185.945508226091</v>
+      </c>
+      <c r="E99">
+        <v>496.1730000000001</v>
+      </c>
+      <c r="F99">
+        <v>873.873</v>
+      </c>
+      <c r="G99">
+        <v>22.4</v>
+      </c>
+      <c r="H99">
+        <v>523.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>43.7</v>
+      </c>
+      <c r="K99">
+        <v>27.5</v>
+      </c>
+      <c r="L99">
+        <v>16.2</v>
+      </c>
+      <c r="M99">
+        <v>208.6808724</v>
+      </c>
+      <c r="N99">
+        <v>-192.4808724</v>
+      </c>
+      <c r="O99">
+        <v>-38.49617448</v>
+      </c>
+      <c r="P99">
+        <v>-153.98469792</v>
+      </c>
+      <c r="Q99">
+        <v>-126.48469792</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.792917472297174</v>
+      </c>
+      <c r="T99">
+        <v>24.59713514513735</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01552609955448892</v>
+      </c>
+      <c r="W99">
+        <v>0.2350923674263881</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.07763049777244457</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2838271205725117</v>
+      </c>
+      <c r="C100">
+        <v>-676.0542462803622</v>
+      </c>
+      <c r="D100">
+        <v>184.4277537196378</v>
+      </c>
+      <c r="E100">
+        <v>505.1820000000001</v>
+      </c>
+      <c r="F100">
+        <v>882.8820000000001</v>
+      </c>
+      <c r="G100">
+        <v>22.4</v>
+      </c>
+      <c r="H100">
+        <v>523.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>43.7</v>
+      </c>
+      <c r="K100">
+        <v>27.5</v>
+      </c>
+      <c r="L100">
+        <v>16.2</v>
+      </c>
+      <c r="M100">
+        <v>210.8322216</v>
+      </c>
+      <c r="N100">
+        <v>-194.6322216</v>
+      </c>
+      <c r="O100">
+        <v>-38.92644432</v>
+      </c>
+      <c r="P100">
+        <v>-155.70577728</v>
+      </c>
+      <c r="Q100">
+        <v>-128.20577728</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.669976208445761</v>
+      </c>
+      <c r="T100">
+        <v>36.89570271770603</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01536766996719822</v>
+      </c>
+      <c r="W100">
+        <v>0.2351302004118331</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.07683834983599103</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2858271205725117</v>
+      </c>
+      <c r="C101">
+        <v>-686.5564244649455</v>
+      </c>
+      <c r="D101">
+        <v>182.9345755350546</v>
+      </c>
+      <c r="E101">
+        <v>514.191</v>
+      </c>
+      <c r="F101">
+        <v>891.8910000000001</v>
+      </c>
+      <c r="G101">
+        <v>22.4</v>
+      </c>
+      <c r="H101">
+        <v>523.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>43.7</v>
+      </c>
+      <c r="K101">
+        <v>27.5</v>
+      </c>
+      <c r="L101">
+        <v>16.2</v>
+      </c>
+      <c r="M101">
+        <v>212.9835708</v>
+      </c>
+      <c r="N101">
+        <v>-196.7835708</v>
+      </c>
+      <c r="O101">
+        <v>-39.35671416</v>
+      </c>
+      <c r="P101">
+        <v>-157.42685664</v>
+      </c>
+      <c r="Q101">
+        <v>-129.92685664</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.301152416891521</v>
+      </c>
+      <c r="T101">
+        <v>73.79140543541206</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01521244097763056</v>
+      </c>
+      <c r="W101">
+        <v>0.2351672690945418</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.07606220488815274</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
